--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A029D6-354D-4D14-ACB6-5DAC0A477B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6766C6-E187-4B06-B797-13D0BD75252E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3825" yWindow="1035" windowWidth="28800" windowHeight="15345" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="40110" yWindow="2250" windowWidth="28800" windowHeight="15345" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
     <sheet name="20260914" sheetId="37" r:id="rId1"/>
@@ -4635,34 +4635,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Mon (14th)</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.51180555555555551</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F2" s="30">
         <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G2" s="28"/>
       <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>0</v>
+        <v>5.3666666666666663</v>
       </c>
       <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>0</v>
+        <v>2.9833333333333334</v>
       </c>
       <c r="J2" s="12">
         <f>H2 + I2 + G2</f>
-        <v>0</v>
-      </c>
-      <c r="K2" s="13" t="str">
+        <v>8.35</v>
+      </c>
+      <c r="K2" s="13">
         <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L2" s="14" t="str">
+        <v>44</v>
+      </c>
+      <c r="L2" s="14">
         <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-21.999999999999979</v>
       </c>
       <c r="M2" s="15"/>
     </row>
@@ -4671,34 +4679,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Tue (15th)</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.5756944444444444</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.60486111111111107</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F3" s="30">
         <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3" s="28"/>
       <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>0</v>
+        <v>6.8999999999999995</v>
       </c>
       <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>0</v>
+        <v>1.4833333333333334</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="13" t="str">
+        <v>8.3833333333333329</v>
+      </c>
+      <c r="K3" s="13">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L3" s="14" t="str">
+        <v>42.000000000000014</v>
+      </c>
+      <c r="L3" s="14">
         <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-23.999999999999972</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -4706,26 +4722,30 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Wed (16th)</v>
       </c>
-      <c r="B4" s="8"/>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
+      <c r="E4" s="8">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F4" s="30">
         <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" s="28"/>
       <c r="H4" s="10">
         <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>0</v>
+        <v>-6.9166666666666661</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="K4" s="13" t="str">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
@@ -4813,15 +4833,15 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>0</v>
+        <v>25.81666666666667</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>0</v>
+        <v>3.5666666666666669</v>
       </c>
       <c r="L7" s="34">
         <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
-        <v>0</v>
+        <v>0.76666666666666583</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -4833,7 +4853,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>40</v>
+        <v>14.18333333333333</v>
       </c>
       <c r="K9" s="26"/>
     </row>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6766C6-E187-4B06-B797-13D0BD75252E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66005647-586C-4E5E-BF0E-2938BE8E9F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40110" yWindow="2250" windowWidth="28800" windowHeight="15345" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="39240" yWindow="2010" windowWidth="28800" windowHeight="15345" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
     <sheet name="20260914" sheetId="37" r:id="rId1"/>
@@ -4725,35 +4725,39 @@
       <c r="B4" s="8">
         <v>0.28819444444444442</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
+      <c r="C4" s="8">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.58333333333333337</v>
+      </c>
       <c r="E4" s="8">
         <v>0.66666666666666663</v>
       </c>
       <c r="F4" s="30">
         <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G4" s="28"/>
       <c r="H4" s="10">
         <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>-6.9166666666666661</v>
+        <v>6.2166666666666686</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>16</v>
+        <v>1.9999999999999982</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>9.0833333333333339</v>
-      </c>
-      <c r="K4" s="13" t="str">
+        <v>8.2166666666666668</v>
+      </c>
+      <c r="K4" s="13">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L4" s="14" t="str">
+        <v>51.999999999999972</v>
+      </c>
+      <c r="L4" s="14">
         <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-14.000000000000007</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -4761,34 +4765,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Thu (17th)</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.51597222222222228</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F5" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" s="28"/>
       <c r="H5" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.6166666666666645</v>
       </c>
       <c r="J5" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K5" s="13" t="str">
+        <v>8.3666666666666636</v>
+      </c>
+      <c r="K5" s="13">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L5" s="14" t="str">
+        <v>43.000000000000085</v>
+      </c>
+      <c r="L5" s="14">
         <f t="shared" si="5"/>
-        <v>-</v>
+        <v>-22.999999999999815</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
@@ -4833,15 +4845,15 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>25.81666666666667</v>
+        <v>33.316666666666663</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>3.5666666666666669</v>
+        <v>1.9833333333333318</v>
       </c>
       <c r="L7" s="34">
         <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
-        <v>0.76666666666666583</v>
+        <v>1.3833333333333295</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -4853,7 +4865,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>14.18333333333333</v>
+        <v>6.6833333333333371</v>
       </c>
       <c r="K9" s="26"/>
     </row>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,48 +8,49 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66005647-586C-4E5E-BF0E-2938BE8E9F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED4C3BC-C0BA-4F10-9879-F99257C5134E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39240" yWindow="2010" windowWidth="28800" windowHeight="15345" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="39690" yWindow="1470" windowWidth="31365" windowHeight="15345" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
-    <sheet name="20260914" sheetId="37" r:id="rId1"/>
-    <sheet name="20260907" sheetId="36" state="hidden" r:id="rId2"/>
-    <sheet name="20260831" sheetId="35" state="hidden" r:id="rId3"/>
-    <sheet name="20260824" sheetId="34" state="hidden" r:id="rId4"/>
-    <sheet name="20260817" sheetId="33" state="hidden" r:id="rId5"/>
-    <sheet name="20260810" sheetId="32" state="hidden" r:id="rId6"/>
-    <sheet name="20260803" sheetId="31" state="hidden" r:id="rId7"/>
-    <sheet name="20260727" sheetId="30" state="hidden" r:id="rId8"/>
-    <sheet name="20260720" sheetId="29" state="hidden" r:id="rId9"/>
-    <sheet name="20260713" sheetId="28" state="hidden" r:id="rId10"/>
-    <sheet name="20260706" sheetId="27" state="hidden" r:id="rId11"/>
-    <sheet name="20260629" sheetId="26" state="hidden" r:id="rId12"/>
-    <sheet name="20260622" sheetId="25" state="hidden" r:id="rId13"/>
-    <sheet name="20260615" sheetId="24" state="hidden" r:id="rId14"/>
-    <sheet name="20260608" sheetId="23" state="hidden" r:id="rId15"/>
-    <sheet name="20260601" sheetId="22" state="hidden" r:id="rId16"/>
-    <sheet name="20260525" sheetId="21" state="hidden" r:id="rId17"/>
-    <sheet name="20260518" sheetId="20" state="hidden" r:id="rId18"/>
-    <sheet name="20260511" sheetId="19" state="hidden" r:id="rId19"/>
-    <sheet name="20260504" sheetId="18" state="hidden" r:id="rId20"/>
-    <sheet name="20260427" sheetId="17" state="hidden" r:id="rId21"/>
-    <sheet name="20260420" sheetId="16" state="hidden" r:id="rId22"/>
-    <sheet name="20260413" sheetId="15" state="hidden" r:id="rId23"/>
-    <sheet name="20260408" sheetId="14" state="hidden" r:id="rId24"/>
-    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId25"/>
-    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId26"/>
-    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId27"/>
-    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId28"/>
-    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId29"/>
-    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId30"/>
-    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId31"/>
-    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId32"/>
-    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId33"/>
-    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId34"/>
-    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId35"/>
-    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId36"/>
-    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId37"/>
+    <sheet name="20260921" sheetId="38" r:id="rId1"/>
+    <sheet name="20260914" sheetId="37" r:id="rId2"/>
+    <sheet name="20260907" sheetId="36" state="hidden" r:id="rId3"/>
+    <sheet name="20260831" sheetId="35" state="hidden" r:id="rId4"/>
+    <sheet name="20260824" sheetId="34" state="hidden" r:id="rId5"/>
+    <sheet name="20260817" sheetId="33" state="hidden" r:id="rId6"/>
+    <sheet name="20260810" sheetId="32" state="hidden" r:id="rId7"/>
+    <sheet name="20260803" sheetId="31" state="hidden" r:id="rId8"/>
+    <sheet name="20260727" sheetId="30" state="hidden" r:id="rId9"/>
+    <sheet name="20260720" sheetId="29" state="hidden" r:id="rId10"/>
+    <sheet name="20260713" sheetId="28" state="hidden" r:id="rId11"/>
+    <sheet name="20260706" sheetId="27" state="hidden" r:id="rId12"/>
+    <sheet name="20260629" sheetId="26" state="hidden" r:id="rId13"/>
+    <sheet name="20260622" sheetId="25" state="hidden" r:id="rId14"/>
+    <sheet name="20260615" sheetId="24" state="hidden" r:id="rId15"/>
+    <sheet name="20260608" sheetId="23" state="hidden" r:id="rId16"/>
+    <sheet name="20260601" sheetId="22" state="hidden" r:id="rId17"/>
+    <sheet name="20260525" sheetId="21" state="hidden" r:id="rId18"/>
+    <sheet name="20260518" sheetId="20" state="hidden" r:id="rId19"/>
+    <sheet name="20260511" sheetId="19" state="hidden" r:id="rId20"/>
+    <sheet name="20260504" sheetId="18" state="hidden" r:id="rId21"/>
+    <sheet name="20260427" sheetId="17" state="hidden" r:id="rId22"/>
+    <sheet name="20260420" sheetId="16" state="hidden" r:id="rId23"/>
+    <sheet name="20260413" sheetId="15" state="hidden" r:id="rId24"/>
+    <sheet name="20260408" sheetId="14" state="hidden" r:id="rId25"/>
+    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId26"/>
+    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId27"/>
+    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId28"/>
+    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId29"/>
+    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId30"/>
+    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId31"/>
+    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId32"/>
+    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId33"/>
+    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId34"/>
+    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId35"/>
+    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId36"/>
+    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId37"/>
+    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId38"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -94,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="25">
   <si>
     <t>In</t>
   </si>
@@ -640,7 +641,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="377">
+  <dxfs count="388">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1455,6 +1456,113 @@
       <fill>
         <patternFill>
           <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4575,7 +4683,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A4D2493-FA26-4C6B-B29B-2869ADDFFA07}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB17A34-8771-4EB9-93AD-612A5096895D}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
@@ -4594,7 +4702,7 @@
     <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="str" cm="1">
         <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>09/14/2026</v>
+        <v>09/21/2026</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -4633,19 +4741,19 @@
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (14th)</v>
+        <v>Mon (21st)</v>
       </c>
       <c r="B2" s="8">
         <v>0.28819444444444442</v>
       </c>
       <c r="C2" s="8">
-        <v>0.51180555555555551</v>
+        <v>0.52569444444444446</v>
       </c>
       <c r="D2" s="8">
-        <v>0.54236111111111107</v>
+        <v>0.55625000000000002</v>
       </c>
       <c r="E2" s="8">
-        <v>0.66666666666666663</v>
+        <v>0.66874999999999996</v>
       </c>
       <c r="F2" s="30">
         <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
@@ -4654,15 +4762,15 @@
       <c r="G2" s="28"/>
       <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>5.3666666666666663</v>
+        <v>5.7000000000000011</v>
       </c>
       <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>2.9833333333333334</v>
+        <v>2.6999999999999984</v>
       </c>
       <c r="J2" s="12">
         <f>H2 + I2 + G2</f>
-        <v>8.35</v>
+        <v>8.3999999999999986</v>
       </c>
       <c r="K2" s="13">
         <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
@@ -4670,143 +4778,123 @@
       </c>
       <c r="L2" s="14">
         <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
+        <v>-24.999999999999915</v>
       </c>
       <c r="M2" s="15"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (15th)</v>
+        <v>Tue (22nd)</v>
       </c>
       <c r="B3" s="8">
         <v>0.28819444444444442</v>
       </c>
-      <c r="C3" s="8">
-        <v>0.5756944444444444</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.60486111111111107</v>
-      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
       <c r="E3" s="8">
         <v>0.66666666666666663</v>
       </c>
       <c r="F3" s="30">
         <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3" s="28"/>
       <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>6.8999999999999995</v>
+        <v>-6.9166666666666661</v>
       </c>
       <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>1.4833333333333334</v>
+        <v>16</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3833333333333329</v>
-      </c>
-      <c r="K3" s="13">
+        <v>9.0833333333333339</v>
+      </c>
+      <c r="K3" s="13" t="str">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>42.000000000000014</v>
-      </c>
-      <c r="L3" s="14">
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L3" s="14" t="str">
         <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-23.999999999999972</v>
+        <v>-</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (16th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.54722222222222228</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.66666666666666663</v>
-      </c>
+        <v>Wed (23rd)</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
       <c r="F4" s="30">
         <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G4" s="28"/>
       <c r="H4" s="10">
         <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>6.2166666666666686</v>
+        <v>0</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>1.9999999999999982</v>
+        <v>0</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>8.2166666666666668</v>
-      </c>
-      <c r="K4" s="13">
+        <v>0</v>
+      </c>
+      <c r="K4" s="13" t="str">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>51.999999999999972</v>
-      </c>
-      <c r="L4" s="14">
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L4" s="14" t="str">
         <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-14.000000000000007</v>
+        <v>-</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (17th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.4861111111111111</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.51597222222222228</v>
-      </c>
-      <c r="E5" s="8">
-        <v>0.66666666666666663</v>
-      </c>
+        <v>Thu (24th)</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
       <c r="F5" s="30">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G5" s="28"/>
       <c r="H5" s="10">
         <f t="shared" si="2"/>
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" si="3"/>
-        <v>3.6166666666666645</v>
+        <v>0</v>
       </c>
       <c r="J5" s="12">
         <f t="shared" si="1"/>
-        <v>8.3666666666666636</v>
-      </c>
-      <c r="K5" s="13">
+        <v>0</v>
+      </c>
+      <c r="K5" s="13" t="str">
         <f t="shared" si="4"/>
-        <v>43.000000000000085</v>
-      </c>
-      <c r="L5" s="14">
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L5" s="14" t="str">
         <f t="shared" si="5"/>
-        <v>-22.999999999999815</v>
+        <v>-</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (18th)</v>
+        <v>Fri (25th)</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -4845,15 +4933,15 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>33.316666666666663</v>
+        <v>17.483333333333334</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>1.9833333333333318</v>
+        <v>4.2666666666666666</v>
       </c>
       <c r="L7" s="34">
         <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
-        <v>1.3833333333333295</v>
+        <v>0.41666666666666524</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -4865,7 +4953,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>6.6833333333333371</v>
+        <v>22.516666666666666</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -4924,45 +5012,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="376" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="387" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="375" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="386" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="374" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="385" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="373" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="384" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="372" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="383" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="371" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="382" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="370" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="381" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="369" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="380" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="368" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="379" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="367" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="378" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="366" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="377" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4972,6 +5060,404 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6BEB823-DE96-4B76-AD70-5A24159396F4}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>07/20/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (20th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.49791666666666667</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66874999999999996</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.0333333333333341</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.3499999999999988</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3833333333333329</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-23.999999999999972</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (21st)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.54583333333333328</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.1833333333333327</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.166666666666667</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.35</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (22nd)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>7.0833333333333348</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>1.2499999999999982</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (23rd)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28">
+        <v>4</v>
+      </c>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>-6.9166666666666661</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.0833333333333339</v>
+      </c>
+      <c r="K5" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L5" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (24th)</v>
+      </c>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10">
+        <v>8</v>
+      </c>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K6" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L6" s="14" t="str">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.15</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>2.7666666666666666</v>
+      </c>
+      <c r="L7" s="34">
+        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
+        <v>1.1166666666666647</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.1499999999999986</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.1499999999999986</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="288" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="287" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="286" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="285" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="284" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="283" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="282" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="281" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="280" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="279" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="278" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8AD448C-2CFD-417A-BD85-6D3F7CCB3F58}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M25"/>
@@ -5378,7 +5864,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB95E3B-E135-478C-8A0A-5E432540CE71}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:M25"/>
@@ -5785,7 +6271,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7975CB53-D379-4DD2-B96A-2E9A2B15DA29}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:M25"/>
@@ -6186,7 +6672,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CCB17B7-31E3-42D5-9A97-21469AA24C23}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:M25"/>
@@ -6587,7 +7073,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7AFBA1B-7343-4E05-A088-EE92C857EAFC}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:M25"/>
@@ -6995,7 +7481,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F536AF-B26B-4088-9F12-A3C7FDB6B0E0}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:M25"/>
@@ -7402,7 +7888,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC499B9-050F-4A63-AD58-B03C062DE40E}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:M25"/>
@@ -7809,7 +8295,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ADA2EDE-7873-4984-BD8B-6BE6DA51A055}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:M25"/>
@@ -8208,7 +8694,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{147CAD13-550A-47AC-814D-87BFC7C1D749}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:M25"/>
@@ -8605,7 +9091,412 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A4D2493-FA26-4C6B-B29B-2869ADDFFA07}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>09/14/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (14th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.51180555555555551</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.3666666666666663</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.9833333333333334</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.35</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (15th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.5756944444444444</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.60486111111111107</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="28"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.8999999999999995</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>1.4833333333333334</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3833333333333329</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>42.000000000000014</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-23.999999999999972</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (16th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>6.2166666666666686</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>1.9999999999999982</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.2166666666666668</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>51.999999999999972</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-14.000000000000007</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (17th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.51597222222222228</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>4.75</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.6166666666666645</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666636</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>43.000000000000085</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-22.999999999999815</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (18th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.53402777777777777</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.0833333333333339</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>3.1833333333333327</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.2666666666666657</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>48.999999999999986</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-16.999999999999943</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.583333333333329</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.1666666666666656</v>
+      </c>
+      <c r="L7" s="34">
+        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
+        <v>1.6666666666666619</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.5833333333333286</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.5833333333333286</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="376" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="375" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="374" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="373" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="372" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="371" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="370" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="369" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="368" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="367" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="366" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{880CC944-ACF2-4B78-8F94-9FEAAB92C701}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:M25"/>
@@ -9008,400 +9899,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39FCE4F4-4177-4ECC-BBBB-6DD7A08CB273}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>09/07/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (7th)</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="28">
-        <v>8</v>
-      </c>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>0</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>0</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8</v>
-      </c>
-      <c r="K2" s="13" t="str">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L2" s="14" t="str">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (8th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.5541666666666667</v>
-      </c>
-      <c r="E3" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>5.5833333333333348</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.6999999999999984</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.2833333333333332</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>47.999999999999986</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-17.999999999999993</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (9th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.50416666666666665</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.53541666666666665</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>5.1833333333333336</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>3.1499999999999995</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (10th)</v>
-      </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28">
-        <v>8</v>
-      </c>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="K5" s="13" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L5" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (11th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.50486111111111109</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.53472222222222221</v>
-      </c>
-      <c r="E6" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.2</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>3.1666666666666661</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="4"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="L6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>40.983333333333327</v>
-      </c>
-      <c r="K7" s="25">
-        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>2.7333333333333334</v>
-      </c>
-      <c r="L7" s="34">
-        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
-        <v>1.0333333333333325</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-0.98333333333332718</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>0.98333333333332718</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="365" priority="3" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="364" priority="4" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="363" priority="8" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="362" priority="9" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="361" priority="10" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="360" priority="11" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="359" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="358" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="357" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="356" priority="6" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="355" priority="7" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4CFE7D-7614-4F7F-B0B0-8B0AD836CA96}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:M25"/>
@@ -9798,7 +10296,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56C38E4F-E691-46C6-97FD-EC7175A0C027}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:M25"/>
@@ -10201,7 +10699,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7461D9D8-918B-4A24-B181-4C0540C55ECF}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:M25"/>
@@ -10604,7 +11102,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3005DEE3-E784-4BAF-9730-AC8A15978DE6}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:M25"/>
@@ -11007,7 +11505,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D473AA26-956E-44CC-A227-92587E57ACBA}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:M25"/>
@@ -11411,7 +11909,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DAA111-5E1D-4B97-9693-D547B2E6E4CE}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:M25"/>
@@ -11815,7 +12313,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E2ECAE-46BA-4924-85FC-E83F2A7590E3}">
   <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:M25"/>
@@ -12219,7 +12717,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCCCED9-7C1F-4E5C-BB14-2542C55B392A}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:M25"/>
@@ -12615,7 +13113,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71775678-8DD4-41DB-BC9F-367C263DFB6D}">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:M25"/>
@@ -13013,7 +13511,400 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39FCE4F4-4177-4ECC-BBBB-6DD7A08CB273}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>09/07/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (7th)</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="28">
+        <v>8</v>
+      </c>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8</v>
+      </c>
+      <c r="K2" s="13" t="str">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L2" s="14" t="str">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (8th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.5541666666666667</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="28"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.5833333333333348</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.6999999999999984</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.2833333333333332</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>47.999999999999986</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-17.999999999999993</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (9th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.50416666666666665</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.53541666666666665</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>5.1833333333333336</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>3.1499999999999995</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (10th)</v>
+      </c>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28">
+        <v>8</v>
+      </c>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K5" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L5" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (11th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.50486111111111109</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.2</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>3.1666666666666661</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>40.983333333333327</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>2.7333333333333334</v>
+      </c>
+      <c r="L7" s="34">
+        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
+        <v>1.0333333333333325</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-0.98333333333332718</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>0.98333333333332718</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="365" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="364" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="363" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="362" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="361" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="360" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="359" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="358" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="357" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="356" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="355" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3D6F94-B8B8-465C-9353-6F78C34B9117}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:M25"/>
@@ -13407,410 +14298,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C93E5BB9-8062-4382-A731-FC67616139D4}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>08/31/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (31st)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.52708333333333335</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.55694444444444446</v>
-      </c>
-      <c r="E2" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>5.7333333333333343</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>2.633333333333332</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (1st)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.54305555555555551</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.57291666666666663</v>
-      </c>
-      <c r="E3" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.1166666666666663</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.25</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (2nd)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.51736111111111116</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.54861111111111116</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>5.5000000000000018</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>2.8333333333333313</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (3rd)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.52708333333333335</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.55763888888888891</v>
-      </c>
-      <c r="E5" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>5.7333333333333343</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>2.6166666666666654</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.35</v>
-      </c>
-      <c r="K5" s="13">
-        <f t="shared" si="4"/>
-        <v>44</v>
-      </c>
-      <c r="L5" s="14">
-        <f t="shared" si="5"/>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (4th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10">
-        <v>4</v>
-      </c>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>-6.9166666666666661</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8.0833333333333339</v>
-      </c>
-      <c r="K6" s="13" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L6" s="14" t="str">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.5</v>
-      </c>
-      <c r="K7" s="25">
-        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>2.0833333333333335</v>
-      </c>
-      <c r="L7" s="34">
-        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
-        <v>1.4833333333333329</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.5</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="354" priority="3" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="353" priority="4" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="352" priority="8" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="351" priority="9" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="350" priority="10" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="349" priority="11" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="348" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="347" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="346" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="345" priority="6" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="344" priority="7" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2022D25-AB37-4043-9F9F-6F62C5CF4383}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:M25"/>
@@ -14187,7 +14675,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAB208D-7788-4F4C-BA6F-08A0CD669B15}">
   <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:M25"/>
@@ -14570,7 +15058,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D776AF6C-2FD4-4B22-9D2F-E02D7E857044}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:M25"/>
@@ -14953,7 +15441,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3377F8F3-7578-415F-8E55-F8837A247A0F}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:M25"/>
@@ -15334,7 +15822,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCD931C-AA06-4404-8DD2-3A1635928042}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:L25"/>
@@ -15685,7 +16173,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:L25"/>
@@ -16036,7 +16524,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:L25"/>
@@ -16387,7 +16875,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:L25"/>
@@ -16739,6 +17227,409 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C93E5BB9-8062-4382-A731-FC67616139D4}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>08/31/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (31st)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.52708333333333335</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.55694444444444446</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.7333333333333343</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.633333333333332</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (1st)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.54305555555555551</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="28"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.1166666666666663</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.25</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (2nd)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.51736111111111116</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>5.5000000000000018</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.8333333333333313</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (3rd)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.52708333333333335</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.55763888888888891</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>5.7333333333333343</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>2.6166666666666654</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (4th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10">
+        <v>4</v>
+      </c>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>-6.9166666666666661</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.0833333333333339</v>
+      </c>
+      <c r="K6" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L6" s="14" t="str">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.5</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>2.0833333333333335</v>
+      </c>
+      <c r="L7" s="34">
+        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
+        <v>1.4833333333333329</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.5</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="354" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="353" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="352" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="351" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="350" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="349" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="348" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="347" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="346" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="345" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="344" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{767FE0DE-E855-4B79-85C0-6CD6FF74CBDD}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -17143,7 +18034,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E46A523-17A0-4C50-9CE8-8BC834C882EC}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -17545,7 +18436,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29ED05D9-F336-4072-952B-730FA495965E}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -17936,7 +18827,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{947F5BDC-A24C-4A68-9554-63E3753A4309}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -18337,7 +19228,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E8092A-444B-4499-9A96-86E4F540520F}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -18738,402 +19629,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6BEB823-DE96-4B76-AD70-5A24159396F4}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>07/20/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (20th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.49791666666666667</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66874999999999996</v>
-      </c>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>5.0333333333333341</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.3499999999999988</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.3833333333333329</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-23.999999999999972</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (21st)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.54583333333333328</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.57638888888888884</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.1833333333333327</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.166666666666667</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.35</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (22nd)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.61458333333333337</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>7.0833333333333348</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>1.2499999999999982</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (23rd)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="9">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28">
-        <v>4</v>
-      </c>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>-6.9166666666666661</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.0833333333333339</v>
-      </c>
-      <c r="K5" s="13" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L5" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (24th)</v>
-      </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10">
-        <v>8</v>
-      </c>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="K6" s="13" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L6" s="14" t="str">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.15</v>
-      </c>
-      <c r="K7" s="25">
-        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>2.7666666666666666</v>
-      </c>
-      <c r="L7" s="34">
-        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
-        <v>1.1166666666666647</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.1499999999999986</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>1.1499999999999986</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="288" priority="3" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="287" priority="4" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="286" priority="8" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="285" priority="9" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="284" priority="10" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="283" priority="11" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="282" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="281" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="280" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="279" priority="6" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="278" priority="7" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED4C3BC-C0BA-4F10-9879-F99257C5134E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548AA828-23CB-42F5-B71A-E6ED1F2E67F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39690" yWindow="1470" windowWidth="31365" windowHeight="15345" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="2565" yWindow="1365" windowWidth="31365" windowHeight="15345" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
     <sheet name="20260921" sheetId="38" r:id="rId1"/>
@@ -4790,35 +4790,39 @@
       <c r="B3" s="8">
         <v>0.28819444444444442</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
+      <c r="C3" s="8">
+        <v>0.5625</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.59444444444444444</v>
+      </c>
       <c r="E3" s="8">
         <v>0.66666666666666663</v>
       </c>
       <c r="F3" s="30">
         <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G3" s="28"/>
       <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>-6.9166666666666661</v>
+        <v>6.5833333333333339</v>
       </c>
       <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>16</v>
+        <v>1.7333333333333325</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>9.0833333333333339</v>
-      </c>
-      <c r="K3" s="13" t="str">
+        <v>8.3166666666666664</v>
+      </c>
+      <c r="K3" s="13">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L3" s="14" t="str">
+        <v>46</v>
+      </c>
+      <c r="L3" s="14">
         <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-19.999999999999986</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -4826,34 +4830,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Wed (23rd)</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.58194444444444449</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.61319444444444449</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F4" s="30">
         <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G4" s="28"/>
       <c r="H4" s="10">
         <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>0</v>
+        <v>7.0500000000000016</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>0</v>
+        <v>1.2833333333333314</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K4" s="13" t="str">
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L4" s="14" t="str">
+        <v>45</v>
+      </c>
+      <c r="L4" s="14">
         <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-20.999999999999929</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -4861,26 +4873,32 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Thu (24th)</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
+      <c r="B5" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="8">
+        <v>0.54166666666666663</v>
+      </c>
       <c r="F5" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G5" s="28"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28">
+        <v>4</v>
+      </c>
       <c r="H5" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J5" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K5" s="13" t="str">
         <f t="shared" si="4"/>
@@ -4933,15 +4951,15 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>17.483333333333334</v>
+        <v>33.049999999999997</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>4.2666666666666666</v>
+        <v>2.75</v>
       </c>
       <c r="L7" s="34">
         <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
-        <v>0.41666666666666524</v>
+        <v>1.0999999999999972</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -4953,7 +4971,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>22.516666666666666</v>
+        <v>6.9500000000000028</v>
       </c>
       <c r="K9" s="26"/>
     </row>

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,49 +8,51 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548AA828-23CB-42F5-B71A-E6ED1F2E67F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86B4C0E-4029-4DC7-8A89-549D0A188C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2565" yWindow="1365" windowWidth="31365" windowHeight="15345" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="4290" yWindow="975" windowWidth="33285" windowHeight="20625" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
-    <sheet name="20260921" sheetId="38" r:id="rId1"/>
-    <sheet name="20260914" sheetId="37" r:id="rId2"/>
-    <sheet name="20260907" sheetId="36" state="hidden" r:id="rId3"/>
-    <sheet name="20260831" sheetId="35" state="hidden" r:id="rId4"/>
-    <sheet name="20260824" sheetId="34" state="hidden" r:id="rId5"/>
-    <sheet name="20260817" sheetId="33" state="hidden" r:id="rId6"/>
-    <sheet name="20260810" sheetId="32" state="hidden" r:id="rId7"/>
-    <sheet name="20260803" sheetId="31" state="hidden" r:id="rId8"/>
-    <sheet name="20260727" sheetId="30" state="hidden" r:id="rId9"/>
-    <sheet name="20260720" sheetId="29" state="hidden" r:id="rId10"/>
-    <sheet name="20260713" sheetId="28" state="hidden" r:id="rId11"/>
-    <sheet name="20260706" sheetId="27" state="hidden" r:id="rId12"/>
-    <sheet name="20260629" sheetId="26" state="hidden" r:id="rId13"/>
-    <sheet name="20260622" sheetId="25" state="hidden" r:id="rId14"/>
-    <sheet name="20260615" sheetId="24" state="hidden" r:id="rId15"/>
-    <sheet name="20260608" sheetId="23" state="hidden" r:id="rId16"/>
-    <sheet name="20260601" sheetId="22" state="hidden" r:id="rId17"/>
-    <sheet name="20260525" sheetId="21" state="hidden" r:id="rId18"/>
-    <sheet name="20260518" sheetId="20" state="hidden" r:id="rId19"/>
-    <sheet name="20260511" sheetId="19" state="hidden" r:id="rId20"/>
-    <sheet name="20260504" sheetId="18" state="hidden" r:id="rId21"/>
-    <sheet name="20260427" sheetId="17" state="hidden" r:id="rId22"/>
-    <sheet name="20260420" sheetId="16" state="hidden" r:id="rId23"/>
-    <sheet name="20260413" sheetId="15" state="hidden" r:id="rId24"/>
-    <sheet name="20260408" sheetId="14" state="hidden" r:id="rId25"/>
-    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId26"/>
-    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId27"/>
-    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId28"/>
-    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId29"/>
-    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId30"/>
-    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId31"/>
-    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId32"/>
-    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId33"/>
-    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId34"/>
-    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId35"/>
-    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId36"/>
-    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId37"/>
-    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId38"/>
+    <sheet name="20261005" sheetId="40" r:id="rId1"/>
+    <sheet name="20260928" sheetId="39" state="hidden" r:id="rId2"/>
+    <sheet name="20260921" sheetId="38" state="hidden" r:id="rId3"/>
+    <sheet name="20260914" sheetId="37" state="hidden" r:id="rId4"/>
+    <sheet name="20260907" sheetId="36" state="hidden" r:id="rId5"/>
+    <sheet name="20260831" sheetId="35" state="hidden" r:id="rId6"/>
+    <sheet name="20260824" sheetId="34" state="hidden" r:id="rId7"/>
+    <sheet name="20260817" sheetId="33" state="hidden" r:id="rId8"/>
+    <sheet name="20260810" sheetId="32" state="hidden" r:id="rId9"/>
+    <sheet name="20260803" sheetId="31" state="hidden" r:id="rId10"/>
+    <sheet name="20260727" sheetId="30" state="hidden" r:id="rId11"/>
+    <sheet name="20260720" sheetId="29" state="hidden" r:id="rId12"/>
+    <sheet name="20260713" sheetId="28" state="hidden" r:id="rId13"/>
+    <sheet name="20260706" sheetId="27" state="hidden" r:id="rId14"/>
+    <sheet name="20260629" sheetId="26" state="hidden" r:id="rId15"/>
+    <sheet name="20260622" sheetId="25" state="hidden" r:id="rId16"/>
+    <sheet name="20260615" sheetId="24" state="hidden" r:id="rId17"/>
+    <sheet name="20260608" sheetId="23" state="hidden" r:id="rId18"/>
+    <sheet name="20260601" sheetId="22" state="hidden" r:id="rId19"/>
+    <sheet name="20260525" sheetId="21" state="hidden" r:id="rId20"/>
+    <sheet name="20260518" sheetId="20" state="hidden" r:id="rId21"/>
+    <sheet name="20260511" sheetId="19" state="hidden" r:id="rId22"/>
+    <sheet name="20260504" sheetId="18" state="hidden" r:id="rId23"/>
+    <sheet name="20260427" sheetId="17" state="hidden" r:id="rId24"/>
+    <sheet name="20260420" sheetId="16" state="hidden" r:id="rId25"/>
+    <sheet name="20260413" sheetId="15" state="hidden" r:id="rId26"/>
+    <sheet name="20260408" sheetId="14" state="hidden" r:id="rId27"/>
+    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId28"/>
+    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId29"/>
+    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId30"/>
+    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId31"/>
+    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId32"/>
+    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId33"/>
+    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId34"/>
+    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId35"/>
+    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId36"/>
+    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId37"/>
+    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId38"/>
+    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId39"/>
+    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId40"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -95,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="25">
   <si>
     <t>In</t>
   </si>
@@ -641,7 +643,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="388">
+  <dxfs count="410">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1456,6 +1458,220 @@
       <fill>
         <patternFill>
           <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4683,7 +4899,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB17A34-8771-4EB9-93AD-612A5096895D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D839D3B-74C1-4606-AD5E-3ACF14EBFDDF}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
@@ -4702,7 +4918,7 @@
     <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="str" cm="1">
         <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>09/21/2026</v>
+        <v>10/05/2026</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -4741,19 +4957,19 @@
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (21st)</v>
+        <v>Mon (5th)</v>
       </c>
       <c r="B2" s="8">
         <v>0.28819444444444442</v>
       </c>
       <c r="C2" s="8">
-        <v>0.52569444444444446</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D2" s="8">
-        <v>0.55625000000000002</v>
+        <v>0.55138888888888893</v>
       </c>
       <c r="E2" s="8">
-        <v>0.66874999999999996</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F2" s="30">
         <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
@@ -4762,15 +4978,15 @@
       <c r="G2" s="28"/>
       <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>5.7000000000000011</v>
+        <v>5.5833333333333348</v>
       </c>
       <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>2.6999999999999984</v>
+        <v>2.7666666666666648</v>
       </c>
       <c r="J2" s="12">
         <f>H2 + I2 + G2</f>
-        <v>8.3999999999999986</v>
+        <v>8.35</v>
       </c>
       <c r="K2" s="13">
         <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
@@ -4778,127 +4994,109 @@
       </c>
       <c r="L2" s="14">
         <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-24.999999999999915</v>
+        <v>-21.999999999999979</v>
       </c>
       <c r="M2" s="15"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (22nd)</v>
+        <v>Tue (6th)</v>
       </c>
       <c r="B3" s="8">
         <v>0.28819444444444442</v>
       </c>
-      <c r="C3" s="8">
-        <v>0.5625</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.59444444444444444</v>
-      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
       <c r="E3" s="8">
         <v>0.66666666666666663</v>
       </c>
       <c r="F3" s="30">
         <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3" s="28"/>
       <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>6.5833333333333339</v>
+        <v>-6.9166666666666661</v>
       </c>
       <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>1.7333333333333325</v>
+        <v>16</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3166666666666664</v>
-      </c>
-      <c r="K3" s="13">
+        <v>9.0833333333333339</v>
+      </c>
+      <c r="K3" s="13" t="str">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>46</v>
-      </c>
-      <c r="L3" s="14">
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L3" s="14" t="str">
         <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-19.999999999999986</v>
+        <v>-</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (23rd)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.58194444444444449</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.61319444444444449</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.66666666666666663</v>
-      </c>
+        <v>Wed (7th)</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
       <c r="F4" s="30">
         <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G4" s="28"/>
       <c r="H4" s="10">
         <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>7.0500000000000016</v>
+        <v>0</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>1.2833333333333314</v>
+        <v>0</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K4" s="13">
+        <v>0</v>
+      </c>
+      <c r="K4" s="13" t="str">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L4" s="14">
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L4" s="14" t="str">
         <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
+        <v>-</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (24th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.375</v>
-      </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="8">
-        <v>0.54166666666666663</v>
-      </c>
+        <v>Thu (8th)</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
       <c r="F5" s="30">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G5" s="28"/>
       <c r="H5" s="10">
         <f t="shared" si="2"/>
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J5" s="12">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K5" s="13" t="str">
         <f t="shared" si="4"/>
@@ -4912,7 +5110,7 @@
     <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (25th)</v>
+        <v>Fri (9th)</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -4951,16 +5149,17 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>33.049999999999997</v>
+        <v>17.433333333333334</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>2.75</v>
+        <v>4.2666666666666666</v>
       </c>
       <c r="L7" s="34">
-        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
-        <v>1.0999999999999972</v>
-      </c>
+        <f>(IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1) * 60</f>
+        <v>21.999999999999979</v>
+      </c>
+      <c r="M7" s="15"/>
     </row>
     <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
@@ -4971,7 +5170,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>6.9500000000000028</v>
+        <v>22.566666666666666</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -5030,45 +5229,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="387" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="409" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="386" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="408" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="385" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="407" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="384" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="406" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="383" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="405" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="382" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="404" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="381" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="403" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="380" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="402" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="379" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="401" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="378" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="400" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="377" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="399" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5078,6 +5277,810 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{947F5BDC-A24C-4A68-9554-63E3753A4309}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>08/03/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (3rd)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.54513888888888884</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66736111111111107</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.4166666666666661</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.9333333333333336</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.35</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (4th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.52430555555555558</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.55277777777777781</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.6666666666666679</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.7333333333333316</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3999999999999986</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>41.000000000000014</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-24.999999999999915</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (5th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.49444444444444446</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.52430555555555558</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>4.9500000000000011</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>3.4166666666666652</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (6th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28">
+        <v>4</v>
+      </c>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>-6.9166666666666661</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.0833333333333339</v>
+      </c>
+      <c r="K5" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L5" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (7th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10">
+        <v>4</v>
+      </c>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>-6.9166666666666661</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.0833333333333339</v>
+      </c>
+      <c r="K6" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L6" s="14" t="str">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.283333333333339</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>2.8499999999999996</v>
+      </c>
+      <c r="L7" s="34">
+        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
+        <v>1.1666666666666652</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.2833333333333385</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.2833333333333385</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="310" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="309" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="308" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="307" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="306" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="305" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="304" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="303" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="302" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="301" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="300" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E8092A-444B-4499-9A96-86E4F540520F}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>07/27/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (27th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.5833333333333348</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.799999999999998</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3833333333333329</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>42.000000000000014</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-23.999999999999972</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (28th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.50208333333333333</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.52986111111111112</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.1333333333333337</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.5333333333333323</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>7.6666666666666661</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>40.000000000000014</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>21.000000000000036</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (29th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.4909722222222222</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.52013888888888893</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28">
+        <v>3</v>
+      </c>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>4.8666666666666671</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>0.51666666666666483</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3833333333333329</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>42.000000000000092</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-23.999999999999972</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (30th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28">
+        <v>4</v>
+      </c>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>-6.9166666666666661</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.0833333333333339</v>
+      </c>
+      <c r="K5" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L5" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (31st)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10">
+        <v>4</v>
+      </c>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>-6.9166666666666661</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.0833333333333339</v>
+      </c>
+      <c r="K6" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L6" s="14" t="str">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>40.6</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>2.9333333333333313</v>
+      </c>
+      <c r="L7" s="34">
+        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
+        <v>0.44999999999999846</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-0.60000000000000142</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>0.60000000000000142</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="299" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="298" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="297" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="296" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="295" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="294" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="293" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="292" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="291" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="290" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="289" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6BEB823-DE96-4B76-AD70-5A24159396F4}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:M25"/>
@@ -5475,7 +6478,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8AD448C-2CFD-417A-BD85-6D3F7CCB3F58}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M25"/>
@@ -5882,7 +6885,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB95E3B-E135-478C-8A0A-5E432540CE71}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:M25"/>
@@ -6289,7 +7292,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7975CB53-D379-4DD2-B96A-2E9A2B15DA29}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:M25"/>
@@ -6690,7 +7693,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CCB17B7-31E3-42D5-9A97-21469AA24C23}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:M25"/>
@@ -7091,7 +8094,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7AFBA1B-7343-4E05-A088-EE92C857EAFC}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:M25"/>
@@ -7499,7 +8502,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F536AF-B26B-4088-9F12-A3C7FDB6B0E0}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:M25"/>
@@ -7906,7 +8909,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC499B9-050F-4A63-AD58-B03C062DE40E}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:M25"/>
@@ -8313,7 +9316,410 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDA9A0F6-C2E7-4667-8D20-B384B9D566A1}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>09/28/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (28th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.47986111111111113</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.51597222222222228</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0.66736111111111107</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.6000000000000014</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.6333333333333311</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.2333333333333325</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>52.000000000000057</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-14.99999999999995</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (29th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.51597222222222228</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.54583333333333328</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="28"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.4666666666666686</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.9000000000000004</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3666666666666689</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>42.999999999999844</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-23.000000000000135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (30th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.5805555555555556</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.66736111111111107</v>
+      </c>
+      <c r="F4" s="30">
+        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>6.2500000000000018</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.0833333333333313</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>46</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (1st)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>5.166666666666667</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.1999999999999993</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (2nd)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10">
+        <v>4</v>
+      </c>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>-9</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K6" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L6" s="14" t="str">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.3</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.9333333333333351</v>
+      </c>
+      <c r="L7" s="34">
+        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
+        <v>1.3666666666666674</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.2999999999999972</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.2999999999999972</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="398" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="397" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="396" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="395" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="394" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="393" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="392" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="391" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="390" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="389" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="388" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ADA2EDE-7873-4984-BD8B-6BE6DA51A055}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:M25"/>
@@ -8712,7 +10118,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{147CAD13-550A-47AC-814D-87BFC7C1D749}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:M25"/>
@@ -9109,412 +10515,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A4D2493-FA26-4C6B-B29B-2869ADDFFA07}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>09/14/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (14th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.51180555555555551</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.54236111111111107</v>
-      </c>
-      <c r="E2" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>5.3666666666666663</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>2.9833333333333334</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.35</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (15th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.5756944444444444</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.60486111111111107</v>
-      </c>
-      <c r="E3" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.8999999999999995</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>1.4833333333333334</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3833333333333329</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>42.000000000000014</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-23.999999999999972</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (16th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.54722222222222228</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>6.2166666666666686</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>1.9999999999999982</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.2166666666666668</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>51.999999999999972</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-14.000000000000007</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (17th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.4861111111111111</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.51597222222222228</v>
-      </c>
-      <c r="E5" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>4.75</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>3.6166666666666645</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3666666666666636</v>
-      </c>
-      <c r="K5" s="13">
-        <f t="shared" si="4"/>
-        <v>43.000000000000085</v>
-      </c>
-      <c r="L5" s="14">
-        <f t="shared" si="5"/>
-        <v>-22.999999999999815</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (18th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.53402777777777777</v>
-      </c>
-      <c r="E6" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.0833333333333339</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>3.1833333333333327</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8.2666666666666657</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="4"/>
-        <v>48.999999999999986</v>
-      </c>
-      <c r="L6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-16.999999999999943</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.583333333333329</v>
-      </c>
-      <c r="K7" s="25">
-        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>1.1666666666666656</v>
-      </c>
-      <c r="L7" s="34">
-        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
-        <v>1.6666666666666619</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.5833333333333286</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>1.5833333333333286</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="376" priority="3" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="375" priority="4" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="374" priority="8" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="373" priority="9" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="372" priority="10" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="371" priority="11" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="370" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="369" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="368" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="367" priority="6" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="366" priority="7" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{880CC944-ACF2-4B78-8F94-9FEAAB92C701}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:M25"/>
@@ -9917,7 +10918,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4CFE7D-7614-4F7F-B0B0-8B0AD836CA96}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:M25"/>
@@ -10314,7 +11315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56C38E4F-E691-46C6-97FD-EC7175A0C027}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:M25"/>
@@ -10717,7 +11718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7461D9D8-918B-4A24-B181-4C0540C55ECF}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:M25"/>
@@ -11120,7 +12121,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3005DEE3-E784-4BAF-9730-AC8A15978DE6}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:M25"/>
@@ -11523,7 +12524,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D473AA26-956E-44CC-A227-92587E57ACBA}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:M25"/>
@@ -11927,7 +12928,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DAA111-5E1D-4B97-9693-D547B2E6E4CE}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:M25"/>
@@ -12331,7 +13332,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E2ECAE-46BA-4924-85FC-E83F2A7590E3}">
   <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:M25"/>
@@ -12735,7 +13736,410 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB17A34-8771-4EB9-93AD-612A5096895D}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>09/21/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (21st)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.52569444444444446</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.55625000000000002</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0.66874999999999996</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.7000000000000011</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.6999999999999984</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3999999999999986</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-24.999999999999915</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (22nd)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.5625</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.59444444444444444</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="28"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.5833333333333339</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>1.7333333333333325</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3166666666666664</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>46</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-19.999999999999986</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (23rd)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.58194444444444449</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.61319444444444449</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>7.0500000000000016</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>1.2833333333333314</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (24th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28">
+        <v>4</v>
+      </c>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>-9</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K5" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L5" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (25th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.50972222222222219</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.3166666666666664</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3166666666666664</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>46</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-19.999999999999986</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.36666666666666</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.9833333333333334</v>
+      </c>
+      <c r="L7" s="34">
+        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
+        <v>1.4333333333333302</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.36666666666666</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.36666666666666</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="387" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="386" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="385" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="384" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="383" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="382" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="381" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="380" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="379" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="378" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="377" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCCCED9-7C1F-4E5C-BB14-2542C55B392A}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:M25"/>
@@ -13131,7 +14535,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71775678-8DD4-41DB-BC9F-367C263DFB6D}">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:M25"/>
@@ -13529,400 +14933,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39FCE4F4-4177-4ECC-BBBB-6DD7A08CB273}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>09/07/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (7th)</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="28">
-        <v>8</v>
-      </c>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>0</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>0</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8</v>
-      </c>
-      <c r="K2" s="13" t="str">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L2" s="14" t="str">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (8th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.5541666666666667</v>
-      </c>
-      <c r="E3" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>5.5833333333333348</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.6999999999999984</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.2833333333333332</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>47.999999999999986</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-17.999999999999993</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (9th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.50416666666666665</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.53541666666666665</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>5.1833333333333336</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>3.1499999999999995</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (10th)</v>
-      </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28">
-        <v>8</v>
-      </c>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="K5" s="13" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L5" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (11th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.50486111111111109</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.53472222222222221</v>
-      </c>
-      <c r="E6" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.2</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>3.1666666666666661</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="4"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="L6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>40.983333333333327</v>
-      </c>
-      <c r="K7" s="25">
-        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>2.7333333333333334</v>
-      </c>
-      <c r="L7" s="34">
-        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
-        <v>1.0333333333333325</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-0.98333333333332718</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>0.98333333333332718</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="365" priority="3" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="364" priority="4" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="363" priority="8" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="362" priority="9" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="361" priority="10" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="360" priority="11" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="359" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="358" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="357" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="356" priority="6" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="355" priority="7" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3D6F94-B8B8-465C-9353-6F78C34B9117}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:M25"/>
@@ -14316,7 +15327,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2022D25-AB37-4043-9F9F-6F62C5CF4383}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:M25"/>
@@ -14693,7 +15704,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAB208D-7788-4F4C-BA6F-08A0CD669B15}">
   <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:M25"/>
@@ -15076,7 +16087,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D776AF6C-2FD4-4B22-9D2F-E02D7E857044}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:M25"/>
@@ -15459,7 +16470,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3377F8F3-7578-415F-8E55-F8837A247A0F}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:M25"/>
@@ -15840,7 +16851,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCD931C-AA06-4404-8DD2-3A1635928042}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:L25"/>
@@ -16191,7 +17202,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:L25"/>
@@ -16542,7 +17553,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:L25"/>
@@ -16893,7 +17904,412 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A4D2493-FA26-4C6B-B29B-2869ADDFFA07}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>09/14/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (14th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.51180555555555551</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.3666666666666663</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.9833333333333334</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.35</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (15th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.5756944444444444</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.60486111111111107</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="28"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.8999999999999995</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>1.4833333333333334</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3833333333333329</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>42.000000000000014</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-23.999999999999972</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (16th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>6.2166666666666686</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>1.9999999999999982</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.2166666666666668</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>51.999999999999972</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-14.000000000000007</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (17th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.51597222222222228</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>4.75</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.6166666666666645</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666636</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>43.000000000000085</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-22.999999999999815</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (18th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.53402777777777777</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.0833333333333339</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>3.1833333333333327</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.2666666666666657</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>48.999999999999986</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-16.999999999999943</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.583333333333329</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.1666666666666656</v>
+      </c>
+      <c r="L7" s="34">
+        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
+        <v>1.6666666666666619</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.5833333333333286</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.5833333333333286</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="376" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="375" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="374" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="373" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="372" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="371" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="370" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="369" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="368" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="367" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="366" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:L25"/>
@@ -17244,7 +18660,400 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39FCE4F4-4177-4ECC-BBBB-6DD7A08CB273}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>09/07/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (7th)</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="28">
+        <v>8</v>
+      </c>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8</v>
+      </c>
+      <c r="K2" s="13" t="str">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L2" s="14" t="str">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (8th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.5541666666666667</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="28"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.5833333333333348</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.6999999999999984</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.2833333333333332</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>47.999999999999986</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-17.999999999999993</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (9th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.50416666666666665</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.53541666666666665</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>5.1833333333333336</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>3.1499999999999995</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (10th)</v>
+      </c>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28">
+        <v>8</v>
+      </c>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K5" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L5" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (11th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.50486111111111109</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.2</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>3.1666666666666661</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>40.983333333333327</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>2.7333333333333334</v>
+      </c>
+      <c r="L7" s="34">
+        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
+        <v>1.0333333333333325</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-0.98333333333332718</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>0.98333333333332718</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="365" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="364" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="363" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="362" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="361" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="360" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="359" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="358" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="357" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="356" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="355" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C93E5BB9-8062-4382-A731-FC67616139D4}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -17647,7 +19456,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{767FE0DE-E855-4B79-85C0-6CD6FF74CBDD}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -18052,7 +19861,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E46A523-17A0-4C50-9CE8-8BC834C882EC}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -18454,7 +20263,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29ED05D9-F336-4072-952B-730FA495965E}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -18843,808 +20652,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{947F5BDC-A24C-4A68-9554-63E3753A4309}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>08/03/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (3rd)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.51388888888888884</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.54513888888888884</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66736111111111107</v>
-      </c>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>5.4166666666666661</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>2.9333333333333336</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.35</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (4th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.52430555555555558</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.55277777777777781</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>5.6666666666666679</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.7333333333333316</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3999999999999986</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>41.000000000000014</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-24.999999999999915</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (5th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.49444444444444446</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.52430555555555558</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>4.9500000000000011</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>3.4166666666666652</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (6th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="9">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28">
-        <v>4</v>
-      </c>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>-6.9166666666666661</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.0833333333333339</v>
-      </c>
-      <c r="K5" s="13" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L5" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (7th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="9">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10">
-        <v>4</v>
-      </c>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>-6.9166666666666661</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8.0833333333333339</v>
-      </c>
-      <c r="K6" s="13" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L6" s="14" t="str">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.283333333333339</v>
-      </c>
-      <c r="K7" s="25">
-        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>2.8499999999999996</v>
-      </c>
-      <c r="L7" s="34">
-        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
-        <v>1.1666666666666652</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.2833333333333385</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>1.2833333333333385</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="310" priority="3" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="309" priority="4" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="308" priority="8" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="307" priority="9" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="306" priority="10" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="305" priority="11" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="304" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="303" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="302" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="301" priority="6" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="300" priority="7" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E8092A-444B-4499-9A96-86E4F540520F}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>07/27/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (27th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>5.5833333333333348</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>2.799999999999998</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.3833333333333329</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>42.000000000000014</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-23.999999999999972</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (28th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.50208333333333333</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.52986111111111112</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.63541666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>5.1333333333333337</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.5333333333333323</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>7.6666666666666661</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>40.000000000000014</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>21.000000000000036</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (29th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.4909722222222222</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.52013888888888893</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28">
-        <v>3</v>
-      </c>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>4.8666666666666671</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>0.51666666666666483</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3833333333333329</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>42.000000000000092</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-23.999999999999972</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (30th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="9">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28">
-        <v>4</v>
-      </c>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>-6.9166666666666661</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.0833333333333339</v>
-      </c>
-      <c r="K5" s="13" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L5" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (31st)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="9">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10">
-        <v>4</v>
-      </c>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>-6.9166666666666661</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8.0833333333333339</v>
-      </c>
-      <c r="K6" s="13" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L6" s="14" t="str">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>40.6</v>
-      </c>
-      <c r="K7" s="25">
-        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>2.9333333333333313</v>
-      </c>
-      <c r="L7" s="34">
-        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
-        <v>0.44999999999999846</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-0.60000000000000142</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>0.60000000000000142</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="299" priority="3" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="298" priority="4" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="297" priority="8" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="296" priority="9" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="295" priority="10" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="294" priority="11" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="293" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="292" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="291" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="290" priority="6" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="289" priority="7" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,51 +8,52 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86B4C0E-4029-4DC7-8A89-549D0A188C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{568FADB6-4A2C-44E6-B2FF-1434CAC5FA75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="975" windowWidth="33285" windowHeight="20625" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="345" yWindow="705" windowWidth="25575" windowHeight="16605" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
-    <sheet name="20261005" sheetId="40" r:id="rId1"/>
-    <sheet name="20260928" sheetId="39" state="hidden" r:id="rId2"/>
-    <sheet name="20260921" sheetId="38" state="hidden" r:id="rId3"/>
-    <sheet name="20260914" sheetId="37" state="hidden" r:id="rId4"/>
-    <sheet name="20260907" sheetId="36" state="hidden" r:id="rId5"/>
-    <sheet name="20260831" sheetId="35" state="hidden" r:id="rId6"/>
-    <sheet name="20260824" sheetId="34" state="hidden" r:id="rId7"/>
-    <sheet name="20260817" sheetId="33" state="hidden" r:id="rId8"/>
-    <sheet name="20260810" sheetId="32" state="hidden" r:id="rId9"/>
-    <sheet name="20260803" sheetId="31" state="hidden" r:id="rId10"/>
-    <sheet name="20260727" sheetId="30" state="hidden" r:id="rId11"/>
-    <sheet name="20260720" sheetId="29" state="hidden" r:id="rId12"/>
-    <sheet name="20260713" sheetId="28" state="hidden" r:id="rId13"/>
-    <sheet name="20260706" sheetId="27" state="hidden" r:id="rId14"/>
-    <sheet name="20260629" sheetId="26" state="hidden" r:id="rId15"/>
-    <sheet name="20260622" sheetId="25" state="hidden" r:id="rId16"/>
-    <sheet name="20260615" sheetId="24" state="hidden" r:id="rId17"/>
-    <sheet name="20260608" sheetId="23" state="hidden" r:id="rId18"/>
-    <sheet name="20260601" sheetId="22" state="hidden" r:id="rId19"/>
-    <sheet name="20260525" sheetId="21" state="hidden" r:id="rId20"/>
-    <sheet name="20260518" sheetId="20" state="hidden" r:id="rId21"/>
-    <sheet name="20260511" sheetId="19" state="hidden" r:id="rId22"/>
-    <sheet name="20260504" sheetId="18" state="hidden" r:id="rId23"/>
-    <sheet name="20260427" sheetId="17" state="hidden" r:id="rId24"/>
-    <sheet name="20260420" sheetId="16" state="hidden" r:id="rId25"/>
-    <sheet name="20260413" sheetId="15" state="hidden" r:id="rId26"/>
-    <sheet name="20260408" sheetId="14" state="hidden" r:id="rId27"/>
-    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId28"/>
-    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId29"/>
-    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId30"/>
-    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId31"/>
-    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId32"/>
-    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId33"/>
-    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId34"/>
-    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId35"/>
-    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId36"/>
-    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId37"/>
-    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId38"/>
-    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId39"/>
-    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId40"/>
+    <sheet name="20261012" sheetId="41" r:id="rId1"/>
+    <sheet name="20261005" sheetId="40" r:id="rId2"/>
+    <sheet name="20260928" sheetId="39" state="hidden" r:id="rId3"/>
+    <sheet name="20260921" sheetId="38" state="hidden" r:id="rId4"/>
+    <sheet name="20260914" sheetId="37" state="hidden" r:id="rId5"/>
+    <sheet name="20260907" sheetId="36" state="hidden" r:id="rId6"/>
+    <sheet name="20260831" sheetId="35" state="hidden" r:id="rId7"/>
+    <sheet name="20260824" sheetId="34" state="hidden" r:id="rId8"/>
+    <sheet name="20260817" sheetId="33" state="hidden" r:id="rId9"/>
+    <sheet name="20260810" sheetId="32" state="hidden" r:id="rId10"/>
+    <sheet name="20260803" sheetId="31" state="hidden" r:id="rId11"/>
+    <sheet name="20260727" sheetId="30" state="hidden" r:id="rId12"/>
+    <sheet name="20260720" sheetId="29" state="hidden" r:id="rId13"/>
+    <sheet name="20260713" sheetId="28" state="hidden" r:id="rId14"/>
+    <sheet name="20260706" sheetId="27" state="hidden" r:id="rId15"/>
+    <sheet name="20260629" sheetId="26" state="hidden" r:id="rId16"/>
+    <sheet name="20260622" sheetId="25" state="hidden" r:id="rId17"/>
+    <sheet name="20260615" sheetId="24" state="hidden" r:id="rId18"/>
+    <sheet name="20260608" sheetId="23" state="hidden" r:id="rId19"/>
+    <sheet name="20260601" sheetId="22" state="hidden" r:id="rId20"/>
+    <sheet name="20260525" sheetId="21" state="hidden" r:id="rId21"/>
+    <sheet name="20260518" sheetId="20" state="hidden" r:id="rId22"/>
+    <sheet name="20260511" sheetId="19" state="hidden" r:id="rId23"/>
+    <sheet name="20260504" sheetId="18" state="hidden" r:id="rId24"/>
+    <sheet name="20260427" sheetId="17" state="hidden" r:id="rId25"/>
+    <sheet name="20260420" sheetId="16" state="hidden" r:id="rId26"/>
+    <sheet name="20260413" sheetId="15" state="hidden" r:id="rId27"/>
+    <sheet name="20260408" sheetId="14" state="hidden" r:id="rId28"/>
+    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId29"/>
+    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId30"/>
+    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId31"/>
+    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId32"/>
+    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId33"/>
+    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId34"/>
+    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId35"/>
+    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId36"/>
+    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId37"/>
+    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId38"/>
+    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId39"/>
+    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId40"/>
+    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId41"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -97,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="25">
   <si>
     <t>In</t>
   </si>
@@ -643,7 +644,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="410">
+  <dxfs count="421">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1458,6 +1459,113 @@
       <fill>
         <patternFill>
           <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4899,7 +5007,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D839D3B-74C1-4606-AD5E-3ACF14EBFDDF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C9CC5C5-F7CB-43C7-9CDC-410BE50A947C}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
@@ -4918,7 +5026,7 @@
     <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="str" cm="1">
         <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>10/05/2026</v>
+        <v>10/12/2026</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -4957,16 +5065,16 @@
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (5th)</v>
+        <v>Mon (12th)</v>
       </c>
       <c r="B2" s="8">
         <v>0.28819444444444442</v>
       </c>
       <c r="C2" s="8">
-        <v>0.52083333333333337</v>
+        <v>0.54513888888888884</v>
       </c>
       <c r="D2" s="8">
-        <v>0.55138888888888893</v>
+        <v>0.57638888888888884</v>
       </c>
       <c r="E2" s="8">
         <v>0.66666666666666663</v>
@@ -4978,90 +5086,98 @@
       <c r="G2" s="28"/>
       <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>5.5833333333333348</v>
+        <v>6.1666666666666661</v>
       </c>
       <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>2.7666666666666648</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="J2" s="12">
         <f>H2 + I2 + G2</f>
-        <v>8.35</v>
+        <v>8.3333333333333321</v>
       </c>
       <c r="K2" s="13">
         <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L2" s="14">
         <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
+        <v>-20.999999999999929</v>
       </c>
       <c r="M2" s="15"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (6th)</v>
+        <v>Tue (13th)</v>
       </c>
       <c r="B3" s="8">
         <v>0.28819444444444442</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
+      <c r="C3" s="8">
+        <v>0.5625</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.59236111111111112</v>
+      </c>
       <c r="E3" s="8">
         <v>0.66666666666666663</v>
       </c>
       <c r="F3" s="30">
         <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G3" s="28"/>
       <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>-6.9166666666666661</v>
+        <v>6.5833333333333339</v>
       </c>
       <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>16</v>
+        <v>1.7833333333333323</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>9.0833333333333339</v>
-      </c>
-      <c r="K3" s="13" t="str">
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K3" s="13">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L3" s="14" t="str">
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L3" s="14">
         <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-23.000000000000028</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (7th)</v>
-      </c>
-      <c r="B4" s="8"/>
+        <v>Wed (14th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
+      <c r="E4" s="8">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F4" s="30">
         <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" s="28"/>
       <c r="H4" s="10">
         <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>0</v>
+        <v>-6.9166666666666661</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="K4" s="13" t="str">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
@@ -5075,7 +5191,7 @@
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (8th)</v>
+        <v>Thu (15th)</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -5110,7 +5226,7 @@
     <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (9th)</v>
+        <v>Fri (16th)</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -5149,15 +5265,15 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>17.433333333333334</v>
+        <v>25.783333333333331</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>4.2666666666666666</v>
+        <v>3.5333333333333332</v>
       </c>
       <c r="L7" s="34">
         <f>(IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1) * 60</f>
-        <v>21.999999999999979</v>
+        <v>43.999999999999957</v>
       </c>
       <c r="M7" s="15"/>
     </row>
@@ -5170,7 +5286,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>22.566666666666666</v>
+        <v>14.216666666666669</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -5229,45 +5345,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="409" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="420" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="408" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="419" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="407" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="418" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="406" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="417" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="405" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="416" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="404" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="415" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="403" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="414" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="402" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="413" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="401" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="412" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="400" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="411" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="399" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="410" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5277,6 +5393,397 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29ED05D9-F336-4072-952B-730FA495965E}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>08/10/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (10th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="28">
+        <v>4</v>
+      </c>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>-6.9166666666666661</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>11</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.0833333333333339</v>
+      </c>
+      <c r="K2" s="13" t="str">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L2" s="14" t="str">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (11th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="28">
+        <v>4</v>
+      </c>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>-6.9166666666666661</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>11</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.0833333333333339</v>
+      </c>
+      <c r="K3" s="13" t="str">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L3" s="14" t="str">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (12th)</v>
+      </c>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28">
+        <v>8</v>
+      </c>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K4" s="13" t="str">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L4" s="14" t="str">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (13th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28">
+        <v>4</v>
+      </c>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>-6.9166666666666661</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.0833333333333339</v>
+      </c>
+      <c r="K5" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L5" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (14th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10">
+        <v>4</v>
+      </c>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>-6.9166666666666661</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.0833333333333339</v>
+      </c>
+      <c r="K6" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L6" s="14" t="str">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>40.333333333333336</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="34">
+        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-0.3333333333333357</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>0.3333333333333357</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="321" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="320" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="319" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="318" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="317" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="316" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="315" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="314" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="313" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="312" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="311" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{947F5BDC-A24C-4A68-9554-63E3753A4309}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5677,7 +6184,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E8092A-444B-4499-9A96-86E4F540520F}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6080,7 +6587,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6BEB823-DE96-4B76-AD70-5A24159396F4}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:M25"/>
@@ -6478,7 +6985,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8AD448C-2CFD-417A-BD85-6D3F7CCB3F58}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M25"/>
@@ -6885,7 +7392,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB95E3B-E135-478C-8A0A-5E432540CE71}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:M25"/>
@@ -7292,7 +7799,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7975CB53-D379-4DD2-B96A-2E9A2B15DA29}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:M25"/>
@@ -7693,7 +8200,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CCB17B7-31E3-42D5-9A97-21469AA24C23}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:M25"/>
@@ -8094,7 +8601,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7AFBA1B-7343-4E05-A088-EE92C857EAFC}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:M25"/>
@@ -8502,7 +9009,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F536AF-B26B-4088-9F12-A3C7FDB6B0E0}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:M25"/>
@@ -8909,7 +9416,413 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D839D3B-74C1-4606-AD5E-3ACF14EBFDDF}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>10/05/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (5th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.55138888888888893</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.5833333333333348</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.7666666666666648</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.35</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (6th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.52361111111111114</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.55486111111111114</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="28"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.6500000000000012</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.6833333333333318</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (7th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.56597222222222221</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>5.916666666666667</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.4166666666666661</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (8th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.56805555555555554</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>6.7166666666666668</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>1.5999999999999996</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3166666666666664</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>46</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-19.999999999999986</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (9th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28958333333333336</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.56805555555555554</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.59861111111111109</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.66805555555555551</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>6.6833333333333318</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>1.6666666666666661</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3499999999999979</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-21.999999999999872</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.683333333333323</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.2666666666666666</v>
+      </c>
+      <c r="L7" s="34">
+        <f>(IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1) * 60</f>
+        <v>105.9999999999997</v>
+      </c>
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.6833333333333229</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.6833333333333229</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="409" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="408" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="407" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="406" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="405" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="404" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="403" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="402" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="401" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="400" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="399" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC499B9-050F-4A63-AD58-B03C062DE40E}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:M25"/>
@@ -9316,410 +10229,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDA9A0F6-C2E7-4667-8D20-B384B9D566A1}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>09/28/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (28th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.47986111111111113</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.51597222222222228</v>
-      </c>
-      <c r="E2" s="8">
-        <v>0.66736111111111107</v>
-      </c>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.6000000000000014</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.6333333333333311</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.2333333333333325</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>52.000000000000057</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-14.99999999999995</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (29th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.51597222222222228</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.54583333333333328</v>
-      </c>
-      <c r="E3" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>5.4666666666666686</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.9000000000000004</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3666666666666689</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>42.999999999999844</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-23.000000000000135</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (30th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.54861111111111116</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.5805555555555556</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.66736111111111107</v>
-      </c>
-      <c r="F4" s="30">
-        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>6.2500000000000018</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>2.0833333333333313</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>46</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (1st)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.50347222222222221</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.53333333333333333</v>
-      </c>
-      <c r="E5" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>5.166666666666667</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>3.1999999999999993</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="K5" s="13">
-        <f t="shared" si="4"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="L5" s="14">
-        <f t="shared" si="5"/>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (2nd)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.375</v>
-      </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="8">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10">
-        <v>4</v>
-      </c>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>-9</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="K6" s="13" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L6" s="14" t="str">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.3</v>
-      </c>
-      <c r="K7" s="25">
-        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>1.9333333333333351</v>
-      </c>
-      <c r="L7" s="34">
-        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
-        <v>1.3666666666666674</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.2999999999999972</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>1.2999999999999972</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="398" priority="3" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="397" priority="4" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="396" priority="8" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="395" priority="9" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="394" priority="10" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="393" priority="11" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="392" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="391" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="390" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="389" priority="6" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="388" priority="7" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ADA2EDE-7873-4984-BD8B-6BE6DA51A055}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:M25"/>
@@ -10118,7 +10628,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{147CAD13-550A-47AC-814D-87BFC7C1D749}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:M25"/>
@@ -10515,7 +11025,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{880CC944-ACF2-4B78-8F94-9FEAAB92C701}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:M25"/>
@@ -10918,7 +11428,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4CFE7D-7614-4F7F-B0B0-8B0AD836CA96}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:M25"/>
@@ -11315,7 +11825,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56C38E4F-E691-46C6-97FD-EC7175A0C027}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:M25"/>
@@ -11718,7 +12228,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7461D9D8-918B-4A24-B181-4C0540C55ECF}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:M25"/>
@@ -12121,7 +12631,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3005DEE3-E784-4BAF-9730-AC8A15978DE6}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:M25"/>
@@ -12524,7 +13034,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D473AA26-956E-44CC-A227-92587E57ACBA}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:M25"/>
@@ -12928,7 +13438,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DAA111-5E1D-4B97-9693-D547B2E6E4CE}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:M25"/>
@@ -13332,7 +13842,410 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDA9A0F6-C2E7-4667-8D20-B384B9D566A1}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>09/28/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (28th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.47986111111111113</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.51597222222222228</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0.66736111111111107</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.6000000000000014</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.6333333333333311</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.2333333333333325</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>52.000000000000057</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-14.99999999999995</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (29th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.51597222222222228</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.54583333333333328</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="28"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.4666666666666686</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.9000000000000004</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3666666666666689</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>42.999999999999844</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-23.000000000000135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (30th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.5805555555555556</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.66736111111111107</v>
+      </c>
+      <c r="F4" s="30">
+        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>6.2500000000000018</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.0833333333333313</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>46</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (1st)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>5.166666666666667</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.1999999999999993</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (2nd)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10">
+        <v>4</v>
+      </c>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>-9</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K6" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L6" s="14" t="str">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.3</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.9333333333333351</v>
+      </c>
+      <c r="L7" s="34">
+        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
+        <v>1.3666666666666674</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.2999999999999972</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.2999999999999972</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="398" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="397" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="396" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="395" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="394" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="393" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="392" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="391" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="390" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="389" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="388" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E2ECAE-46BA-4924-85FC-E83F2A7590E3}">
   <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:M25"/>
@@ -13736,410 +14649,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB17A34-8771-4EB9-93AD-612A5096895D}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>09/21/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (21st)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.52569444444444446</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.55625000000000002</v>
-      </c>
-      <c r="E2" s="8">
-        <v>0.66874999999999996</v>
-      </c>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>5.7000000000000011</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>2.6999999999999984</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.3999999999999986</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-24.999999999999915</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (22nd)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.5625</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.59444444444444444</v>
-      </c>
-      <c r="E3" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.5833333333333339</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>1.7333333333333325</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3166666666666664</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>46</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-19.999999999999986</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (23rd)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.58194444444444449</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.61319444444444449</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>7.0500000000000016</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>1.2833333333333314</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (24th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.375</v>
-      </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="8">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28">
-        <v>4</v>
-      </c>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>-9</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="K5" s="13" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L5" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (25th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.50972222222222219</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="E6" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.3166666666666664</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3166666666666664</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="4"/>
-        <v>46</v>
-      </c>
-      <c r="L6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-19.999999999999986</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.36666666666666</v>
-      </c>
-      <c r="K7" s="25">
-        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>1.9833333333333334</v>
-      </c>
-      <c r="L7" s="34">
-        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
-        <v>1.4333333333333302</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.36666666666666</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>1.36666666666666</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="387" priority="3" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="386" priority="4" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="385" priority="8" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="384" priority="9" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="383" priority="10" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="382" priority="11" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="381" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="380" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="379" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="378" priority="6" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="377" priority="7" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCCCED9-7C1F-4E5C-BB14-2542C55B392A}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:M25"/>
@@ -14535,7 +15045,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71775678-8DD4-41DB-BC9F-367C263DFB6D}">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:M25"/>
@@ -14933,7 +15443,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3D6F94-B8B8-465C-9353-6F78C34B9117}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:M25"/>
@@ -15327,7 +15837,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2022D25-AB37-4043-9F9F-6F62C5CF4383}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:M25"/>
@@ -15704,7 +16214,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAB208D-7788-4F4C-BA6F-08A0CD669B15}">
   <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:M25"/>
@@ -16087,7 +16597,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D776AF6C-2FD4-4B22-9D2F-E02D7E857044}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:M25"/>
@@ -16470,7 +16980,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3377F8F3-7578-415F-8E55-F8837A247A0F}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:M25"/>
@@ -16851,7 +17361,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCD931C-AA06-4404-8DD2-3A1635928042}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:L25"/>
@@ -17202,7 +17712,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:L25"/>
@@ -17553,7 +18063,410 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB17A34-8771-4EB9-93AD-612A5096895D}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>09/21/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (21st)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.52569444444444446</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.55625000000000002</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0.66874999999999996</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.7000000000000011</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.6999999999999984</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3999999999999986</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-24.999999999999915</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (22nd)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.5625</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.59444444444444444</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="28"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.5833333333333339</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>1.7333333333333325</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3166666666666664</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>46</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-19.999999999999986</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (23rd)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.58194444444444449</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.61319444444444449</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>7.0500000000000016</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>1.2833333333333314</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (24th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28">
+        <v>4</v>
+      </c>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>-9</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K5" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L5" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (25th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.50972222222222219</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.3166666666666664</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3166666666666664</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>46</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-19.999999999999986</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.36666666666666</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.9833333333333334</v>
+      </c>
+      <c r="L7" s="34">
+        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
+        <v>1.4333333333333302</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.36666666666666</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.36666666666666</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="387" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="386" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="385" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="384" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="383" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="382" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="381" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="380" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="379" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="378" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="377" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:L25"/>
@@ -17904,412 +18817,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A4D2493-FA26-4C6B-B29B-2869ADDFFA07}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>09/14/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (14th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.51180555555555551</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.54236111111111107</v>
-      </c>
-      <c r="E2" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>5.3666666666666663</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>2.9833333333333334</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.35</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (15th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.5756944444444444</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.60486111111111107</v>
-      </c>
-      <c r="E3" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.8999999999999995</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>1.4833333333333334</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3833333333333329</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>42.000000000000014</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-23.999999999999972</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (16th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.54722222222222228</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>6.2166666666666686</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>1.9999999999999982</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.2166666666666668</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>51.999999999999972</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-14.000000000000007</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (17th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.4861111111111111</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.51597222222222228</v>
-      </c>
-      <c r="E5" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>4.75</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>3.6166666666666645</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3666666666666636</v>
-      </c>
-      <c r="K5" s="13">
-        <f t="shared" si="4"/>
-        <v>43.000000000000085</v>
-      </c>
-      <c r="L5" s="14">
-        <f t="shared" si="5"/>
-        <v>-22.999999999999815</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (18th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.53402777777777777</v>
-      </c>
-      <c r="E6" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.0833333333333339</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>3.1833333333333327</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8.2666666666666657</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="4"/>
-        <v>48.999999999999986</v>
-      </c>
-      <c r="L6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-16.999999999999943</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.583333333333329</v>
-      </c>
-      <c r="K7" s="25">
-        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>1.1666666666666656</v>
-      </c>
-      <c r="L7" s="34">
-        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
-        <v>1.6666666666666619</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.5833333333333286</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>1.5833333333333286</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="376" priority="3" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="375" priority="4" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="374" priority="8" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="373" priority="9" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="372" priority="10" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="371" priority="11" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="370" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="369" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="368" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="367" priority="6" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="366" priority="7" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:L25"/>
@@ -18661,6 +19169,411 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A4D2493-FA26-4C6B-B29B-2869ADDFFA07}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>09/14/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (14th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.51180555555555551</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.54236111111111107</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.3666666666666663</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.9833333333333334</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.35</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (15th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.5756944444444444</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.60486111111111107</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="28"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.8999999999999995</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>1.4833333333333334</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3833333333333329</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>42.000000000000014</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-23.999999999999972</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (16th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.54722222222222228</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>6.2166666666666686</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>1.9999999999999982</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.2166666666666668</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>51.999999999999972</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-14.000000000000007</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (17th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.51597222222222228</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>4.75</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.6166666666666645</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666636</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>43.000000000000085</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-22.999999999999815</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (18th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.53402777777777777</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.0833333333333339</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>3.1833333333333327</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.2666666666666657</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>48.999999999999986</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-16.999999999999943</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.583333333333329</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.1666666666666656</v>
+      </c>
+      <c r="L7" s="34">
+        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
+        <v>1.6666666666666619</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.5833333333333286</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.5833333333333286</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="376" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="375" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="374" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="373" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="372" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="371" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="370" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="369" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="368" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="367" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="366" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39FCE4F4-4177-4ECC-BBBB-6DD7A08CB273}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -19053,7 +19966,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C93E5BB9-8062-4382-A731-FC67616139D4}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -19456,7 +20369,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{767FE0DE-E855-4B79-85C0-6CD6FF74CBDD}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -19861,7 +20774,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E46A523-17A0-4C50-9CE8-8BC834C882EC}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -20261,395 +21174,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29ED05D9-F336-4072-952B-730FA495965E}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>08/10/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (10th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="9">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="28">
-        <v>4</v>
-      </c>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>-6.9166666666666661</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>11</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.0833333333333339</v>
-      </c>
-      <c r="K2" s="13" t="str">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L2" s="14" t="str">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (11th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="9">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="28">
-        <v>4</v>
-      </c>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>-6.9166666666666661</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>11</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.0833333333333339</v>
-      </c>
-      <c r="K3" s="13" t="str">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L3" s="14" t="str">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (12th)</v>
-      </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28">
-        <v>8</v>
-      </c>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>0</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="K4" s="13" t="str">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L4" s="14" t="str">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (13th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="9">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28">
-        <v>4</v>
-      </c>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>-6.9166666666666661</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.0833333333333339</v>
-      </c>
-      <c r="K5" s="13" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L5" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (14th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="9">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10">
-        <v>4</v>
-      </c>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>-6.9166666666666661</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8.0833333333333339</v>
-      </c>
-      <c r="K6" s="13" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L6" s="14" t="str">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>40.333333333333336</v>
-      </c>
-      <c r="K7" s="25">
-        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="L7" s="34">
-        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-0.3333333333333357</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>0.3333333333333357</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="321" priority="3" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="320" priority="4" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="319" priority="8" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="318" priority="9" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="317" priority="10" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="316" priority="11" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="315" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="314" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="313" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="312" priority="6" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="311" priority="7" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{568FADB6-4A2C-44E6-B2FF-1434CAC5FA75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE667E5-0EA9-402B-80B9-45257C3178C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="705" windowWidth="25575" windowHeight="16605" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="38745" yWindow="360" windowWidth="30435" windowHeight="16605" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
     <sheet name="20261012" sheetId="41" r:id="rId1"/>
@@ -5157,35 +5157,39 @@
       <c r="B4" s="8">
         <v>0.28819444444444442</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
+      <c r="C4" s="8">
+        <v>0.56527777777777777</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.59652777777777777</v>
+      </c>
       <c r="E4" s="8">
         <v>0.66666666666666663</v>
       </c>
       <c r="F4" s="30">
         <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G4" s="28"/>
       <c r="H4" s="10">
         <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>-6.9166666666666661</v>
+        <v>6.65</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>16</v>
+        <v>1.6833333333333327</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>9.0833333333333339</v>
-      </c>
-      <c r="K4" s="13" t="str">
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L4" s="14" t="str">
+        <v>45</v>
+      </c>
+      <c r="L4" s="14">
         <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-20.999999999999929</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -5193,34 +5197,42 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Thu (15th)</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.49166666666666664</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F5" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" s="28"/>
       <c r="H5" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.8833333333333329</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.4499999999999984</v>
       </c>
       <c r="J5" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K5" s="13" t="str">
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K5" s="13">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L5" s="14" t="str">
+        <v>45.000000000000078</v>
+      </c>
+      <c r="L5" s="14">
         <f t="shared" si="5"/>
-        <v>-</v>
+        <v>-20.999999999999929</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
@@ -5228,26 +5240,30 @@
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
         <v>Fri (16th)</v>
       </c>
-      <c r="B6" s="8"/>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
+      <c r="E6" s="8">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F6" s="30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10">
         <f>SUM(C6 - B6) * 24</f>
-        <v>0</v>
+        <v>-6.9166666666666661</v>
       </c>
       <c r="I6" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J6" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9.0833333333333339</v>
       </c>
       <c r="K6" s="13" t="str">
         <f t="shared" si="4"/>
@@ -5265,15 +5281,15 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>25.783333333333331</v>
+        <v>42.449999999999996</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>3.5333333333333332</v>
+        <v>2.0333333333333319</v>
       </c>
       <c r="L7" s="34">
         <f>(IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1) * 60</f>
-        <v>43.999999999999957</v>
+        <v>85.999999999999815</v>
       </c>
       <c r="M7" s="15"/>
     </row>
@@ -5286,7 +5302,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>14.216666666666669</v>
+        <v>-2.4499999999999957</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -5294,9 +5310,9 @@
       <c r="I10" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="25" t="str">
+      <c r="J10" s="25">
         <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>-</v>
+        <v>2.4499999999999957</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE667E5-0EA9-402B-80B9-45257C3178C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA135967-8F14-4A59-A74D-A95741DFF00D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38745" yWindow="360" windowWidth="30435" windowHeight="16605" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="39090" yWindow="705" windowWidth="30435" windowHeight="16605" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
     <sheet name="20261012" sheetId="41" r:id="rId1"/>
@@ -5243,35 +5243,39 @@
       <c r="B6" s="8">
         <v>0.28819444444444442</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="8">
+        <v>0.56319444444444444</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.59375</v>
+      </c>
       <c r="E6" s="8">
         <v>0.66666666666666663</v>
       </c>
       <c r="F6" s="30">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10">
         <f>SUM(C6 - B6) * 24</f>
-        <v>-6.9166666666666661</v>
+        <v>6.6000000000000005</v>
       </c>
       <c r="I6" s="11">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>1.7499999999999991</v>
       </c>
       <c r="J6" s="12">
         <f t="shared" si="1"/>
-        <v>9.0833333333333339</v>
-      </c>
-      <c r="K6" s="13" t="str">
+        <v>8.35</v>
+      </c>
+      <c r="K6" s="13">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L6" s="14" t="str">
+        <v>44</v>
+      </c>
+      <c r="L6" s="14">
         <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-</v>
+        <v>-21.999999999999979</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
@@ -5281,15 +5285,15 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>42.449999999999996</v>
+        <v>41.716666666666661</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>2.0333333333333319</v>
+        <v>1.2999999999999985</v>
       </c>
       <c r="L7" s="34">
         <f>(IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1) * 60</f>
-        <v>85.999999999999815</v>
+        <v>107.9999999999998</v>
       </c>
       <c r="M7" s="15"/>
     </row>
@@ -5302,7 +5306,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>-2.4499999999999957</v>
+        <v>-1.7166666666666615</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -5312,7 +5316,7 @@
       </c>
       <c r="J10" s="25">
         <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>2.4499999999999957</v>
+        <v>1.7166666666666615</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">

--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -1,59 +1,60 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA135967-8F14-4A59-A74D-A95741DFF00D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6408E111-144B-44F2-A16A-7EA1BC0F6F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39090" yWindow="705" windowWidth="30435" windowHeight="16605" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="3855" yWindow="780" windowWidth="30435" windowHeight="16605" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
-    <sheet name="20261012" sheetId="41" r:id="rId1"/>
-    <sheet name="20261005" sheetId="40" r:id="rId2"/>
-    <sheet name="20260928" sheetId="39" state="hidden" r:id="rId3"/>
-    <sheet name="20260921" sheetId="38" state="hidden" r:id="rId4"/>
-    <sheet name="20260914" sheetId="37" state="hidden" r:id="rId5"/>
-    <sheet name="20260907" sheetId="36" state="hidden" r:id="rId6"/>
-    <sheet name="20260831" sheetId="35" state="hidden" r:id="rId7"/>
-    <sheet name="20260824" sheetId="34" state="hidden" r:id="rId8"/>
-    <sheet name="20260817" sheetId="33" state="hidden" r:id="rId9"/>
-    <sheet name="20260810" sheetId="32" state="hidden" r:id="rId10"/>
-    <sheet name="20260803" sheetId="31" state="hidden" r:id="rId11"/>
-    <sheet name="20260727" sheetId="30" state="hidden" r:id="rId12"/>
-    <sheet name="20260720" sheetId="29" state="hidden" r:id="rId13"/>
-    <sheet name="20260713" sheetId="28" state="hidden" r:id="rId14"/>
-    <sheet name="20260706" sheetId="27" state="hidden" r:id="rId15"/>
-    <sheet name="20260629" sheetId="26" state="hidden" r:id="rId16"/>
-    <sheet name="20260622" sheetId="25" state="hidden" r:id="rId17"/>
-    <sheet name="20260615" sheetId="24" state="hidden" r:id="rId18"/>
-    <sheet name="20260608" sheetId="23" state="hidden" r:id="rId19"/>
-    <sheet name="20260601" sheetId="22" state="hidden" r:id="rId20"/>
-    <sheet name="20260525" sheetId="21" state="hidden" r:id="rId21"/>
-    <sheet name="20260518" sheetId="20" state="hidden" r:id="rId22"/>
-    <sheet name="20260511" sheetId="19" state="hidden" r:id="rId23"/>
-    <sheet name="20260504" sheetId="18" state="hidden" r:id="rId24"/>
-    <sheet name="20260427" sheetId="17" state="hidden" r:id="rId25"/>
-    <sheet name="20260420" sheetId="16" state="hidden" r:id="rId26"/>
-    <sheet name="20260413" sheetId="15" state="hidden" r:id="rId27"/>
-    <sheet name="20260408" sheetId="14" state="hidden" r:id="rId28"/>
-    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId29"/>
-    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId30"/>
-    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId31"/>
-    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId32"/>
-    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId33"/>
-    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId34"/>
-    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId35"/>
-    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId36"/>
-    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId37"/>
-    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId38"/>
-    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId39"/>
-    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId40"/>
-    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId41"/>
+    <sheet name="20261019" sheetId="42" r:id="rId1"/>
+    <sheet name="20261012" sheetId="41" r:id="rId2"/>
+    <sheet name="20261005" sheetId="40" r:id="rId3"/>
+    <sheet name="20260928" sheetId="39" state="hidden" r:id="rId4"/>
+    <sheet name="20260921" sheetId="38" state="hidden" r:id="rId5"/>
+    <sheet name="20260914" sheetId="37" state="hidden" r:id="rId6"/>
+    <sheet name="20260907" sheetId="36" state="hidden" r:id="rId7"/>
+    <sheet name="20260831" sheetId="35" state="hidden" r:id="rId8"/>
+    <sheet name="20260824" sheetId="34" state="hidden" r:id="rId9"/>
+    <sheet name="20260817" sheetId="33" state="hidden" r:id="rId10"/>
+    <sheet name="20260810" sheetId="32" state="hidden" r:id="rId11"/>
+    <sheet name="20260803" sheetId="31" state="hidden" r:id="rId12"/>
+    <sheet name="20260727" sheetId="30" state="hidden" r:id="rId13"/>
+    <sheet name="20260720" sheetId="29" state="hidden" r:id="rId14"/>
+    <sheet name="20260713" sheetId="28" state="hidden" r:id="rId15"/>
+    <sheet name="20260706" sheetId="27" state="hidden" r:id="rId16"/>
+    <sheet name="20260629" sheetId="26" state="hidden" r:id="rId17"/>
+    <sheet name="20260622" sheetId="25" state="hidden" r:id="rId18"/>
+    <sheet name="20260615" sheetId="24" state="hidden" r:id="rId19"/>
+    <sheet name="20260608" sheetId="23" state="hidden" r:id="rId20"/>
+    <sheet name="20260601" sheetId="22" state="hidden" r:id="rId21"/>
+    <sheet name="20260525" sheetId="21" state="hidden" r:id="rId22"/>
+    <sheet name="20260518" sheetId="20" state="hidden" r:id="rId23"/>
+    <sheet name="20260511" sheetId="19" state="hidden" r:id="rId24"/>
+    <sheet name="20260504" sheetId="18" state="hidden" r:id="rId25"/>
+    <sheet name="20260427" sheetId="17" state="hidden" r:id="rId26"/>
+    <sheet name="20260420" sheetId="16" state="hidden" r:id="rId27"/>
+    <sheet name="20260413" sheetId="15" state="hidden" r:id="rId28"/>
+    <sheet name="20260408" sheetId="14" state="hidden" r:id="rId29"/>
+    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId30"/>
+    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId31"/>
+    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId32"/>
+    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId33"/>
+    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId34"/>
+    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId35"/>
+    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId36"/>
+    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId37"/>
+    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId38"/>
+    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId39"/>
+    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId40"/>
+    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId41"/>
+    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId42"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -98,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="25">
   <si>
     <t>In</t>
   </si>
@@ -644,7 +645,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="421">
+  <dxfs count="432">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1459,6 +1460,113 @@
       <fill>
         <patternFill>
           <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5007,7 +5115,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C9CC5C5-F7CB-43C7-9CDC-410BE50A947C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F36C4EC-552F-449B-B5CA-C6BB35D1D75B}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
@@ -5026,7 +5134,7 @@
     <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="str" cm="1">
         <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>10/12/2026</v>
+        <v>10/19/2026</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -5065,16 +5173,16 @@
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (12th)</v>
+        <v>Mon (19th)</v>
       </c>
       <c r="B2" s="8">
         <v>0.28819444444444442</v>
       </c>
       <c r="C2" s="8">
-        <v>0.54513888888888884</v>
+        <v>0.5625</v>
       </c>
       <c r="D2" s="8">
-        <v>0.57638888888888884</v>
+        <v>0.59375</v>
       </c>
       <c r="E2" s="8">
         <v>0.66666666666666663</v>
@@ -5086,11 +5194,11 @@
       <c r="G2" s="28"/>
       <c r="H2" s="10">
         <f>SUM(C2 - B2) * 24</f>
-        <v>6.1666666666666661</v>
+        <v>6.5833333333333339</v>
       </c>
       <c r="I2" s="11">
         <f>SUM(E2 - D2) * 24</f>
-        <v>2.166666666666667</v>
+        <v>1.7499999999999991</v>
       </c>
       <c r="J2" s="12">
         <f>H2 + I2 + G2</f>
@@ -5109,16 +5217,16 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (13th)</v>
+        <v>Tue (20th)</v>
       </c>
       <c r="B3" s="8">
         <v>0.28819444444444442</v>
       </c>
       <c r="C3" s="8">
-        <v>0.5625</v>
+        <v>0.56319444444444444</v>
       </c>
       <c r="D3" s="8">
-        <v>0.59236111111111112</v>
+        <v>0.59375</v>
       </c>
       <c r="E3" s="8">
         <v>0.66666666666666663</v>
@@ -5130,41 +5238,41 @@
       <c r="G3" s="28"/>
       <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>6.5833333333333339</v>
+        <v>6.6000000000000005</v>
       </c>
       <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>1.7833333333333323</v>
+        <v>1.7499999999999991</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3666666666666671</v>
+        <v>8.35</v>
       </c>
       <c r="K3" s="13">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
+        <v>44</v>
       </c>
       <c r="L3" s="14">
         <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
+        <v>-21.999999999999979</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (14th)</v>
+        <v>Wed (21st)</v>
       </c>
       <c r="B4" s="8">
         <v>0.28819444444444442</v>
       </c>
       <c r="C4" s="8">
-        <v>0.56527777777777777</v>
+        <v>0.56319444444444444</v>
       </c>
       <c r="D4" s="8">
-        <v>0.59652777777777777</v>
+        <v>0.59375</v>
       </c>
       <c r="E4" s="8">
-        <v>0.66666666666666663</v>
+        <v>0.66319444444444442</v>
       </c>
       <c r="F4" s="30">
         <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
@@ -5173,109 +5281,97 @@
       <c r="G4" s="28"/>
       <c r="H4" s="10">
         <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>6.65</v>
+        <v>6.6000000000000005</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>1.6833333333333327</v>
+        <v>1.6666666666666661</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
+        <v>8.2666666666666657</v>
       </c>
       <c r="K4" s="13">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L4" s="14">
         <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
+        <v>-16.999999999999943</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (15th)</v>
+        <v>Thu (22nd)</v>
       </c>
       <c r="B5" s="8">
         <v>0.28819444444444442</v>
       </c>
-      <c r="C5" s="8">
-        <v>0.49166666666666664</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.5229166666666667</v>
-      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
       <c r="E5" s="8">
         <v>0.66666666666666663</v>
       </c>
       <c r="F5" s="30">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5" s="28"/>
       <c r="H5" s="10">
         <f t="shared" si="2"/>
-        <v>4.8833333333333329</v>
+        <v>-6.9166666666666661</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" si="3"/>
-        <v>3.4499999999999984</v>
+        <v>16</v>
       </c>
       <c r="J5" s="12">
         <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K5" s="13">
+        <v>9.0833333333333339</v>
+      </c>
+      <c r="K5" s="13" t="str">
         <f t="shared" si="4"/>
-        <v>45.000000000000078</v>
-      </c>
-      <c r="L5" s="14">
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L5" s="14" t="str">
         <f t="shared" si="5"/>
-        <v>-20.999999999999929</v>
+        <v>-</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (16th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.56319444444444444</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.59375</v>
-      </c>
-      <c r="E6" s="8">
-        <v>0.66666666666666663</v>
-      </c>
+        <v>Fri (23rd)</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
       <c r="F6" s="30">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10">
         <f>SUM(C6 - B6) * 24</f>
-        <v>6.6000000000000005</v>
+        <v>0</v>
       </c>
       <c r="I6" s="11">
         <f t="shared" si="3"/>
-        <v>1.7499999999999991</v>
+        <v>0</v>
       </c>
       <c r="J6" s="12">
         <f t="shared" si="1"/>
-        <v>8.35</v>
-      </c>
-      <c r="K6" s="13">
+        <v>0</v>
+      </c>
+      <c r="K6" s="13" t="str">
         <f t="shared" si="4"/>
-        <v>44</v>
-      </c>
-      <c r="L6" s="14">
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L6" s="14" t="str">
         <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
+        <v>-</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
@@ -5285,15 +5381,15 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>41.716666666666661</v>
+        <v>34.033333333333331</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>1.2999999999999985</v>
+        <v>2.7833333333333332</v>
       </c>
       <c r="L7" s="34">
         <f>(IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1) * 60</f>
-        <v>107.9999999999998</v>
+        <v>59.999999999999851</v>
       </c>
       <c r="M7" s="15"/>
     </row>
@@ -5306,7 +5402,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>-1.7166666666666615</v>
+        <v>5.9666666666666686</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -5314,9 +5410,9 @@
       <c r="I10" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="25">
+      <c r="J10" s="25" t="str">
         <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>1.7166666666666615</v>
+        <v>-</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -5365,45 +5461,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="420" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="431" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="419" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="430" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="418" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="429" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="417" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="428" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="416" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="427" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="415" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="426" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="414" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="425" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="413" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="424" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="412" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="423" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="411" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="422" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="410" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="421" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5413,6 +5509,408 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E46A523-17A0-4C50-9CE8-8BC834C882EC}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>08/17/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (17th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.46388888888888891</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.50138888888888888</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.2166666666666677</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.9666666666666659</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.1833333333333336</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>53.999999999999972</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-12.000000000000014</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (18th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.53194444444444444</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.56319444444444444</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="28"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.8500000000000005</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.4833333333333325</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (19th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <v>2</v>
+      </c>
+      <c r="G4" s="28">
+        <v>4</v>
+      </c>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>-12</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>16</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K4" s="13" t="str">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L4" s="14" t="str">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (20th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.55347222222222225</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>6.366666666666668</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>1.9999999999999982</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (21st)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.57916666666666672</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>6.2500000000000018</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>2.0999999999999979</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.233333333333334</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.9000000000000006</v>
+      </c>
+      <c r="L7" s="34">
+        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
+        <v>1.2999999999999992</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.2333333333333343</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.2333333333333343</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="332" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="331" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="330" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="329" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="328" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="327" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="326" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="325" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="324" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="323" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="322" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29ED05D9-F336-4072-952B-730FA495965E}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5803,7 +6301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{947F5BDC-A24C-4A68-9554-63E3753A4309}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6204,7 +6702,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E8092A-444B-4499-9A96-86E4F540520F}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6607,7 +7105,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6BEB823-DE96-4B76-AD70-5A24159396F4}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:M25"/>
@@ -7005,7 +7503,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8AD448C-2CFD-417A-BD85-6D3F7CCB3F58}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M25"/>
@@ -7412,7 +7910,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB95E3B-E135-478C-8A0A-5E432540CE71}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:M25"/>
@@ -7819,7 +8317,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7975CB53-D379-4DD2-B96A-2E9A2B15DA29}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:M25"/>
@@ -8220,7 +8718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CCB17B7-31E3-42D5-9A97-21469AA24C23}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:M25"/>
@@ -8621,7 +9119,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7AFBA1B-7343-4E05-A088-EE92C857EAFC}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:M25"/>
@@ -9029,7 +9527,413 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C9CC5C5-F7CB-43C7-9CDC-410BE50A947C}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>10/12/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (12th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.54513888888888884</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>6.1666666666666661</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.166666666666667</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (13th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.5625</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.59236111111111112</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="28"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.5833333333333339</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>1.7833333333333323</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (14th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.56527777777777777</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.59652777777777777</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>6.65</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>1.6833333333333327</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (15th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.49166666666666664</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>4.8833333333333329</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.4499999999999984</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>45.000000000000078</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (16th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.56319444444444444</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.59375</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>6.6000000000000005</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>1.7499999999999991</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.716666666666661</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.2999999999999985</v>
+      </c>
+      <c r="L7" s="34">
+        <f>(IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1) * 60</f>
+        <v>107.9999999999998</v>
+      </c>
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.7166666666666615</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.7166666666666615</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="420" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="419" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="418" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="417" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="416" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="415" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="414" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="413" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="412" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="411" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="410" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F536AF-B26B-4088-9F12-A3C7FDB6B0E0}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:M25"/>
@@ -9436,413 +10340,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D839D3B-74C1-4606-AD5E-3ACF14EBFDDF}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>10/05/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (5th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.55138888888888893</v>
-      </c>
-      <c r="E2" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>5.5833333333333348</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>2.7666666666666648</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.35</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (6th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.52361111111111114</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.55486111111111114</v>
-      </c>
-      <c r="E3" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>5.6500000000000012</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.6833333333333318</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (7th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.53472222222222221</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.56597222222222221</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>5.916666666666667</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>2.4166666666666661</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (8th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.56805555555555554</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.6</v>
-      </c>
-      <c r="E5" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>6.7166666666666668</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>1.5999999999999996</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3166666666666664</v>
-      </c>
-      <c r="K5" s="13">
-        <f t="shared" si="4"/>
-        <v>46</v>
-      </c>
-      <c r="L5" s="14">
-        <f t="shared" si="5"/>
-        <v>-19.999999999999986</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (9th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28958333333333336</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.56805555555555554</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.59861111111111109</v>
-      </c>
-      <c r="E6" s="8">
-        <v>0.66805555555555551</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>6.6833333333333318</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>1.6666666666666661</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3499999999999979</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="4"/>
-        <v>44</v>
-      </c>
-      <c r="L6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-21.999999999999872</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.683333333333323</v>
-      </c>
-      <c r="K7" s="25">
-        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>1.2666666666666666</v>
-      </c>
-      <c r="L7" s="34">
-        <f>(IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1) * 60</f>
-        <v>105.9999999999997</v>
-      </c>
-      <c r="M7" s="15"/>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.6833333333333229</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>1.6833333333333229</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="409" priority="3" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="408" priority="4" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="407" priority="8" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="406" priority="9" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="405" priority="10" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="404" priority="11" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="403" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="402" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="401" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="400" priority="6" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="399" priority="7" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC499B9-050F-4A63-AD58-B03C062DE40E}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:M25"/>
@@ -10249,7 +10747,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ADA2EDE-7873-4984-BD8B-6BE6DA51A055}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:M25"/>
@@ -10648,7 +11146,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{147CAD13-550A-47AC-814D-87BFC7C1D749}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:M25"/>
@@ -11045,7 +11543,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{880CC944-ACF2-4B78-8F94-9FEAAB92C701}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:M25"/>
@@ -11448,7 +11946,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4CFE7D-7614-4F7F-B0B0-8B0AD836CA96}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:M25"/>
@@ -11845,7 +12343,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56C38E4F-E691-46C6-97FD-EC7175A0C027}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:M25"/>
@@ -12248,7 +12746,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7461D9D8-918B-4A24-B181-4C0540C55ECF}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:M25"/>
@@ -12651,7 +13149,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3005DEE3-E784-4BAF-9730-AC8A15978DE6}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:M25"/>
@@ -13054,7 +13552,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D473AA26-956E-44CC-A227-92587E57ACBA}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:M25"/>
@@ -13458,7 +13956,413 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D839D3B-74C1-4606-AD5E-3ACF14EBFDDF}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>10/05/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (5th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.55138888888888893</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.5833333333333348</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.7666666666666648</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.35</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (6th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.52361111111111114</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.55486111111111114</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="28"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.6500000000000012</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.6833333333333318</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (7th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.56597222222222221</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>5.916666666666667</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.4166666666666661</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (8th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.56805555555555554</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>6.7166666666666668</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>1.5999999999999996</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3166666666666664</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>46</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-19.999999999999986</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (9th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28958333333333336</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.56805555555555554</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.59861111111111109</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.66805555555555551</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>6.6833333333333318</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>1.6666666666666661</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3499999999999979</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-21.999999999999872</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.683333333333323</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.2666666666666666</v>
+      </c>
+      <c r="L7" s="34">
+        <f>(IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1) * 60</f>
+        <v>105.9999999999997</v>
+      </c>
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.6833333333333229</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.6833333333333229</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="409" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="408" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="407" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="406" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="405" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="404" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="403" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="402" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="401" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="400" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="399" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DAA111-5E1D-4B97-9693-D547B2E6E4CE}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:M25"/>
@@ -13862,410 +14766,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDA9A0F6-C2E7-4667-8D20-B384B9D566A1}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>09/28/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (28th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.47986111111111113</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.51597222222222228</v>
-      </c>
-      <c r="E2" s="8">
-        <v>0.66736111111111107</v>
-      </c>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.6000000000000014</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.6333333333333311</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.2333333333333325</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>52.000000000000057</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-14.99999999999995</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (29th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.51597222222222228</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.54583333333333328</v>
-      </c>
-      <c r="E3" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>5.4666666666666686</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.9000000000000004</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3666666666666689</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>42.999999999999844</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-23.000000000000135</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (30th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.54861111111111116</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.5805555555555556</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.66736111111111107</v>
-      </c>
-      <c r="F4" s="30">
-        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>6.2500000000000018</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>2.0833333333333313</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>46</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (1st)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.50347222222222221</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.53333333333333333</v>
-      </c>
-      <c r="E5" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>5.166666666666667</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>3.1999999999999993</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="K5" s="13">
-        <f t="shared" si="4"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="L5" s="14">
-        <f t="shared" si="5"/>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (2nd)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.375</v>
-      </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="8">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10">
-        <v>4</v>
-      </c>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>-9</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="K6" s="13" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L6" s="14" t="str">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.3</v>
-      </c>
-      <c r="K7" s="25">
-        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>1.9333333333333351</v>
-      </c>
-      <c r="L7" s="34">
-        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
-        <v>1.3666666666666674</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.2999999999999972</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>1.2999999999999972</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="398" priority="3" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="397" priority="4" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="396" priority="8" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="395" priority="9" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="394" priority="10" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="393" priority="11" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="392" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="391" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="390" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="389" priority="6" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="388" priority="7" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E2ECAE-46BA-4924-85FC-E83F2A7590E3}">
   <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:M25"/>
@@ -14669,7 +15170,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCCCED9-7C1F-4E5C-BB14-2542C55B392A}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:M25"/>
@@ -15065,7 +15566,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71775678-8DD4-41DB-BC9F-367C263DFB6D}">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:M25"/>
@@ -15463,7 +15964,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3D6F94-B8B8-465C-9353-6F78C34B9117}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:M25"/>
@@ -15857,7 +16358,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2022D25-AB37-4043-9F9F-6F62C5CF4383}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:M25"/>
@@ -16234,7 +16735,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAB208D-7788-4F4C-BA6F-08A0CD669B15}">
   <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:M25"/>
@@ -16617,7 +17118,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D776AF6C-2FD4-4B22-9D2F-E02D7E857044}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:M25"/>
@@ -17000,7 +17501,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3377F8F3-7578-415F-8E55-F8837A247A0F}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:M25"/>
@@ -17381,7 +17882,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCD931C-AA06-4404-8DD2-3A1635928042}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:L25"/>
@@ -17732,7 +18233,410 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDA9A0F6-C2E7-4667-8D20-B384B9D566A1}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>09/28/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (28th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.47986111111111113</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.51597222222222228</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0.66736111111111107</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.6000000000000014</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.6333333333333311</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.2333333333333325</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>52.000000000000057</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-14.99999999999995</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (29th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.51597222222222228</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.54583333333333328</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="28"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.4666666666666686</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.9000000000000004</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3666666666666689</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>42.999999999999844</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-23.000000000000135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (30th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.5805555555555556</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.66736111111111107</v>
+      </c>
+      <c r="F4" s="30">
+        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>6.2500000000000018</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.0833333333333313</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>46</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (1st)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>5.166666666666667</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.1999999999999993</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (2nd)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10">
+        <v>4</v>
+      </c>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>-9</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K6" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L6" s="14" t="str">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.3</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.9333333333333351</v>
+      </c>
+      <c r="L7" s="34">
+        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
+        <v>1.3666666666666674</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.2999999999999972</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.2999999999999972</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="398" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="397" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="396" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="395" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="394" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="393" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="392" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="391" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="390" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="389" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="388" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:L25"/>
@@ -18083,410 +18987,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB17A34-8771-4EB9-93AD-612A5096895D}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>09/21/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (21st)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.52569444444444446</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.55625000000000002</v>
-      </c>
-      <c r="E2" s="8">
-        <v>0.66874999999999996</v>
-      </c>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>5.7000000000000011</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>2.6999999999999984</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.3999999999999986</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-24.999999999999915</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (22nd)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.5625</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.59444444444444444</v>
-      </c>
-      <c r="E3" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.5833333333333339</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>1.7333333333333325</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3166666666666664</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>46</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-19.999999999999986</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (23rd)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.58194444444444449</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.61319444444444449</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>7.0500000000000016</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>1.2833333333333314</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (24th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.375</v>
-      </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="8">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28">
-        <v>4</v>
-      </c>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>-9</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="K5" s="13" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L5" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (25th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.50972222222222219</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="E6" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.3166666666666664</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3166666666666664</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="4"/>
-        <v>46</v>
-      </c>
-      <c r="L6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-19.999999999999986</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.36666666666666</v>
-      </c>
-      <c r="K7" s="25">
-        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>1.9833333333333334</v>
-      </c>
-      <c r="L7" s="34">
-        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
-        <v>1.4333333333333302</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.36666666666666</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>1.36666666666666</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="387" priority="3" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="386" priority="4" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="385" priority="8" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="384" priority="9" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="383" priority="10" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="382" priority="11" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="381" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="380" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="379" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="378" priority="6" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="377" priority="7" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:L25"/>
@@ -18837,7 +19338,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:L25"/>
@@ -19189,6 +19690,409 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB17A34-8771-4EB9-93AD-612A5096895D}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>09/21/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (21st)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.52569444444444446</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.55625000000000002</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0.66874999999999996</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.7000000000000011</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.6999999999999984</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3999999999999986</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-24.999999999999915</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (22nd)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.5625</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.59444444444444444</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="28"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.5833333333333339</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>1.7333333333333325</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3166666666666664</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>46</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-19.999999999999986</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (23rd)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.58194444444444449</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.61319444444444449</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>7.0500000000000016</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>1.2833333333333314</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (24th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28">
+        <v>4</v>
+      </c>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>-9</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K5" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L5" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (25th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.50972222222222219</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.3166666666666664</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3166666666666664</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>46</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-19.999999999999986</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.36666666666666</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.9833333333333334</v>
+      </c>
+      <c r="L7" s="34">
+        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
+        <v>1.4333333333333302</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.36666666666666</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.36666666666666</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="387" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="386" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="385" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="384" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="383" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="382" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="381" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="380" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="379" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="378" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="377" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A4D2493-FA26-4C6B-B29B-2869ADDFFA07}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -19593,7 +20497,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39FCE4F4-4177-4ECC-BBBB-6DD7A08CB273}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -19986,7 +20890,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C93E5BB9-8062-4382-A731-FC67616139D4}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -20389,7 +21293,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{767FE0DE-E855-4B79-85C0-6CD6FF74CBDD}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -20792,406 +21696,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E46A523-17A0-4C50-9CE8-8BC834C882EC}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>08/17/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (17th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.46388888888888891</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.50138888888888888</v>
-      </c>
-      <c r="E2" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.2166666666666677</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.9666666666666659</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.1833333333333336</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>53.999999999999972</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-12.000000000000014</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (18th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.53194444444444444</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.56319444444444444</v>
-      </c>
-      <c r="E3" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>5.8500000000000005</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.4833333333333325</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (19th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <v>2</v>
-      </c>
-      <c r="G4" s="28">
-        <v>4</v>
-      </c>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>-12</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>16</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="K4" s="13" t="str">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L4" s="14" t="str">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (20th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.55347222222222225</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="E5" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>6.366666666666668</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>1.9999999999999982</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="K5" s="13">
-        <f t="shared" si="4"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="L5" s="14">
-        <f t="shared" si="5"/>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (21st)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.54861111111111116</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.57916666666666672</v>
-      </c>
-      <c r="E6" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>6.2500000000000018</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>2.0999999999999979</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8.35</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="4"/>
-        <v>44</v>
-      </c>
-      <c r="L6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.233333333333334</v>
-      </c>
-      <c r="K7" s="25">
-        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>1.9000000000000006</v>
-      </c>
-      <c r="L7" s="34">
-        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
-        <v>1.2999999999999992</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.2333333333333343</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>1.2333333333333343</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="332" priority="3" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="331" priority="4" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="330" priority="8" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="329" priority="9" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="328" priority="10" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="327" priority="11" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="326" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="325" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="324" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="323" priority="6" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="322" priority="7" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Time_Tracking/WorkHours_Calculator_2026.xlsx
+++ b/Time_Tracking/WorkHours_Calculator_2026.xlsx
@@ -8,53 +8,54 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositories\PubDev\Time_Tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6408E111-144B-44F2-A16A-7EA1BC0F6F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8064912-9922-4032-AC2B-193712A55D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3855" yWindow="780" windowWidth="30435" windowHeight="16605" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="15345" xr2:uid="{F0FEE646-CA9E-4872-A8E1-626BBC6FFE10}"/>
   </bookViews>
   <sheets>
-    <sheet name="20261019" sheetId="42" r:id="rId1"/>
-    <sheet name="20261012" sheetId="41" r:id="rId2"/>
-    <sheet name="20261005" sheetId="40" r:id="rId3"/>
-    <sheet name="20260928" sheetId="39" state="hidden" r:id="rId4"/>
-    <sheet name="20260921" sheetId="38" state="hidden" r:id="rId5"/>
-    <sheet name="20260914" sheetId="37" state="hidden" r:id="rId6"/>
-    <sheet name="20260907" sheetId="36" state="hidden" r:id="rId7"/>
-    <sheet name="20260831" sheetId="35" state="hidden" r:id="rId8"/>
-    <sheet name="20260824" sheetId="34" state="hidden" r:id="rId9"/>
-    <sheet name="20260817" sheetId="33" state="hidden" r:id="rId10"/>
-    <sheet name="20260810" sheetId="32" state="hidden" r:id="rId11"/>
-    <sheet name="20260803" sheetId="31" state="hidden" r:id="rId12"/>
-    <sheet name="20260727" sheetId="30" state="hidden" r:id="rId13"/>
-    <sheet name="20260720" sheetId="29" state="hidden" r:id="rId14"/>
-    <sheet name="20260713" sheetId="28" state="hidden" r:id="rId15"/>
-    <sheet name="20260706" sheetId="27" state="hidden" r:id="rId16"/>
-    <sheet name="20260629" sheetId="26" state="hidden" r:id="rId17"/>
-    <sheet name="20260622" sheetId="25" state="hidden" r:id="rId18"/>
-    <sheet name="20260615" sheetId="24" state="hidden" r:id="rId19"/>
-    <sheet name="20260608" sheetId="23" state="hidden" r:id="rId20"/>
-    <sheet name="20260601" sheetId="22" state="hidden" r:id="rId21"/>
-    <sheet name="20260525" sheetId="21" state="hidden" r:id="rId22"/>
-    <sheet name="20260518" sheetId="20" state="hidden" r:id="rId23"/>
-    <sheet name="20260511" sheetId="19" state="hidden" r:id="rId24"/>
-    <sheet name="20260504" sheetId="18" state="hidden" r:id="rId25"/>
-    <sheet name="20260427" sheetId="17" state="hidden" r:id="rId26"/>
-    <sheet name="20260420" sheetId="16" state="hidden" r:id="rId27"/>
-    <sheet name="20260413" sheetId="15" state="hidden" r:id="rId28"/>
-    <sheet name="20260408" sheetId="14" state="hidden" r:id="rId29"/>
-    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId30"/>
-    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId31"/>
-    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId32"/>
-    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId33"/>
-    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId34"/>
-    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId35"/>
-    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId36"/>
-    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId37"/>
-    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId38"/>
-    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId39"/>
-    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId40"/>
-    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId41"/>
-    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId42"/>
+    <sheet name="20261026" sheetId="43" r:id="rId1"/>
+    <sheet name="20261019" sheetId="42" r:id="rId2"/>
+    <sheet name="20261012" sheetId="41" r:id="rId3"/>
+    <sheet name="20261005" sheetId="40" r:id="rId4"/>
+    <sheet name="20260928" sheetId="39" state="hidden" r:id="rId5"/>
+    <sheet name="20260921" sheetId="38" state="hidden" r:id="rId6"/>
+    <sheet name="20260914" sheetId="37" state="hidden" r:id="rId7"/>
+    <sheet name="20260907" sheetId="36" state="hidden" r:id="rId8"/>
+    <sheet name="20260831" sheetId="35" state="hidden" r:id="rId9"/>
+    <sheet name="20260824" sheetId="34" state="hidden" r:id="rId10"/>
+    <sheet name="20260817" sheetId="33" state="hidden" r:id="rId11"/>
+    <sheet name="20260810" sheetId="32" state="hidden" r:id="rId12"/>
+    <sheet name="20260803" sheetId="31" state="hidden" r:id="rId13"/>
+    <sheet name="20260727" sheetId="30" state="hidden" r:id="rId14"/>
+    <sheet name="20260720" sheetId="29" state="hidden" r:id="rId15"/>
+    <sheet name="20260713" sheetId="28" state="hidden" r:id="rId16"/>
+    <sheet name="20260706" sheetId="27" state="hidden" r:id="rId17"/>
+    <sheet name="20260629" sheetId="26" state="hidden" r:id="rId18"/>
+    <sheet name="20260622" sheetId="25" state="hidden" r:id="rId19"/>
+    <sheet name="20260615" sheetId="24" state="hidden" r:id="rId20"/>
+    <sheet name="20260608" sheetId="23" state="hidden" r:id="rId21"/>
+    <sheet name="20260601" sheetId="22" state="hidden" r:id="rId22"/>
+    <sheet name="20260525" sheetId="21" state="hidden" r:id="rId23"/>
+    <sheet name="20260518" sheetId="20" state="hidden" r:id="rId24"/>
+    <sheet name="20260511" sheetId="19" state="hidden" r:id="rId25"/>
+    <sheet name="20260504" sheetId="18" state="hidden" r:id="rId26"/>
+    <sheet name="20260427" sheetId="17" state="hidden" r:id="rId27"/>
+    <sheet name="20260420" sheetId="16" state="hidden" r:id="rId28"/>
+    <sheet name="20260413" sheetId="15" state="hidden" r:id="rId29"/>
+    <sheet name="20260408" sheetId="14" state="hidden" r:id="rId30"/>
+    <sheet name="20260330" sheetId="13" state="hidden" r:id="rId31"/>
+    <sheet name="20260323" sheetId="12" state="hidden" r:id="rId32"/>
+    <sheet name="20260316" sheetId="11" state="hidden" r:id="rId33"/>
+    <sheet name="20260309" sheetId="10" state="hidden" r:id="rId34"/>
+    <sheet name="20260302" sheetId="9" state="hidden" r:id="rId35"/>
+    <sheet name="20260223" sheetId="8" state="hidden" r:id="rId36"/>
+    <sheet name="20260216" sheetId="7" state="hidden" r:id="rId37"/>
+    <sheet name="20260209" sheetId="6" state="hidden" r:id="rId38"/>
+    <sheet name="20260202" sheetId="5" state="hidden" r:id="rId39"/>
+    <sheet name="20260126" sheetId="4" state="hidden" r:id="rId40"/>
+    <sheet name="20260119" sheetId="3" state="hidden" r:id="rId41"/>
+    <sheet name="20260112" sheetId="2" state="hidden" r:id="rId42"/>
+    <sheet name="20260105" sheetId="1" state="hidden" r:id="rId43"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -99,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="25">
   <si>
     <t>In</t>
   </si>
@@ -645,7 +646,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="432">
+  <dxfs count="443">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1460,6 +1461,113 @@
       <fill>
         <patternFill>
           <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5115,7 +5223,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F36C4EC-552F-449B-B5CA-C6BB35D1D75B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{642F67AB-6171-49EB-82A4-F752103F1665}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
@@ -5134,7 +5242,7 @@
     <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="str" cm="1">
         <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>10/19/2026</v>
+        <v>10/26/2026</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -5173,7 +5281,7 @@
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (19th)</v>
+        <v>Mon (26th)</v>
       </c>
       <c r="B2" s="8">
         <v>0.28819444444444442</v>
@@ -5217,118 +5325,102 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (20th)</v>
+        <v>Tue (27th)</v>
       </c>
       <c r="B3" s="8">
         <v>0.28819444444444442</v>
       </c>
-      <c r="C3" s="8">
-        <v>0.56319444444444444</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.59375</v>
-      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
       <c r="E3" s="8">
         <v>0.66666666666666663</v>
       </c>
       <c r="F3" s="30">
         <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3" s="28"/>
       <c r="H3" s="10">
         <f>SUM(C3 - B3) * 24</f>
-        <v>6.6000000000000005</v>
+        <v>-6.9166666666666661</v>
       </c>
       <c r="I3" s="11">
         <f>SUM(E3 - D3) * 24</f>
-        <v>1.7499999999999991</v>
+        <v>16</v>
       </c>
       <c r="J3" s="12">
         <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.35</v>
-      </c>
-      <c r="K3" s="13">
+        <v>9.0833333333333339</v>
+      </c>
+      <c r="K3" s="13" t="str">
         <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L3" s="14">
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L3" s="14" t="str">
         <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
+        <v>-</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (21st)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.56319444444444444</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.59375</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.66319444444444442</v>
-      </c>
+        <v>Wed (28th)</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
       <c r="F4" s="30">
         <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G4" s="28"/>
       <c r="H4" s="10">
         <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>6.6000000000000005</v>
+        <v>0</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>1.6666666666666661</v>
+        <v>0</v>
       </c>
       <c r="J4" s="12">
         <f t="shared" si="1"/>
-        <v>8.2666666666666657</v>
-      </c>
-      <c r="K4" s="13">
+        <v>0</v>
+      </c>
+      <c r="K4" s="13" t="str">
         <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L4" s="14">
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L4" s="14" t="str">
         <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-16.999999999999943</v>
+        <v>-</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (22nd)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
+        <v>Thu (29th)</v>
+      </c>
+      <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="8">
-        <v>0.66666666666666663</v>
-      </c>
+      <c r="E5" s="8"/>
       <c r="F5" s="30">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" s="28"/>
       <c r="H5" s="10">
         <f t="shared" si="2"/>
-        <v>-6.9166666666666661</v>
+        <v>0</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J5" s="12">
         <f t="shared" si="1"/>
-        <v>9.0833333333333339</v>
+        <v>0</v>
       </c>
       <c r="K5" s="13" t="str">
         <f t="shared" si="4"/>
@@ -5342,7 +5434,7 @@
     <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16" t="str">
         <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (23rd)</v>
+        <v>Fri (30th)</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -5381,15 +5473,15 @@
       </c>
       <c r="J7" s="22">
         <f>SUM(J2:J6)</f>
-        <v>34.033333333333331</v>
+        <v>17.416666666666664</v>
       </c>
       <c r="K7" s="25">
         <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>2.7833333333333332</v>
+        <v>4.25</v>
       </c>
       <c r="L7" s="34">
         <f>(IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1) * 60</f>
-        <v>59.999999999999851</v>
+        <v>20.999999999999929</v>
       </c>
       <c r="M7" s="15"/>
     </row>
@@ -5402,7 +5494,7 @@
       </c>
       <c r="J9" s="25">
         <f>40-J7</f>
-        <v>5.9666666666666686</v>
+        <v>22.583333333333336</v>
       </c>
       <c r="K9" s="26"/>
     </row>
@@ -5461,45 +5553,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="431" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="442" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="430" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="441" priority="4" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="429" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="440" priority="8" operator="greaterThan">
       <formula>7.99999999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="428" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="439" priority="9" operator="lessThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="427" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="438" priority="10" operator="lessThan">
       <formula>40</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="426" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="437" priority="11" operator="greaterThan">
       <formula>39.999999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="425" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="436" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="424" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="435" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="423" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="434" priority="5" operator="equal">
       <formula>"-"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="422" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="433" priority="6" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="421" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="432" priority="7" operator="lessThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5509,6 +5601,411 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{767FE0DE-E855-4B79-85C0-6CD6FF74CBDD}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>08/24/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (24th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.50763888888888886</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.53888888888888886</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.2666666666666666</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.0666666666666664</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (25th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.49930555555555556</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.53055555555555556</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="28"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.0666666666666673</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>3.2666666666666657</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (26th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.5541666666666667</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>5.6333333333333346</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.6999999999999984</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (27th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.5131944444444444</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.54374999999999996</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>5.3999999999999995</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>2.95</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (28th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.51458333333333328</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.54513888888888884</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.71736111111111112</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>5.4333333333333327</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>4.1333333333333346</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>9.5666666666666664</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-94.999999999999986</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>42.916666666666657</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.2833333333333334</v>
+      </c>
+      <c r="L7" s="34">
+        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
+        <v>2.999999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-2.9166666666666572</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>2.9166666666666572</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="343" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="342" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="341" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="340" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="339" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="338" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="337" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="336" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="335" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="334" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="333" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E46A523-17A0-4C50-9CE8-8BC834C882EC}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -5910,7 +6407,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29ED05D9-F336-4072-952B-730FA495965E}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6301,7 +6798,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{947F5BDC-A24C-4A68-9554-63E3753A4309}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -6702,7 +7199,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E8092A-444B-4499-9A96-86E4F540520F}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -7105,7 +7602,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6BEB823-DE96-4B76-AD70-5A24159396F4}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:M25"/>
@@ -7503,7 +8000,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8AD448C-2CFD-417A-BD85-6D3F7CCB3F58}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M25"/>
@@ -7910,7 +8407,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB95E3B-E135-478C-8A0A-5E432540CE71}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:M25"/>
@@ -8317,7 +8814,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7975CB53-D379-4DD2-B96A-2E9A2B15DA29}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:M25"/>
@@ -8718,7 +9215,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CCB17B7-31E3-42D5-9A97-21469AA24C23}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:M25"/>
@@ -9119,7 +9616,413 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F36C4EC-552F-449B-B5CA-C6BB35D1D75B}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>10/19/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (19th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.5625</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.59375</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>6.5833333333333339</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>1.7499999999999991</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (20th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.56319444444444444</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.59375</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="28"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.6000000000000005</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>1.7499999999999991</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.35</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (21st)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.56319444444444444</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.59375</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.66319444444444442</v>
+      </c>
+      <c r="F4" s="30">
+        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>6.6000000000000005</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>1.6666666666666661</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.2666666666666657</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-16.999999999999943</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (22nd)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.5625</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.59375</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>6.5833333333333339</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>1.7499999999999991</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>45</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (23rd)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.5625</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.59444444444444444</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>6.5833333333333339</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>1.7333333333333325</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3166666666666664</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>46</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-19.999999999999986</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.599999999999994</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.2666666666666666</v>
+      </c>
+      <c r="L7" s="34">
+        <f>(IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1) * 60</f>
+        <v>100.99999999999976</v>
+      </c>
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.5999999999999943</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.5999999999999943</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="431" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="430" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="429" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="428" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="427" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="426" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="425" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="424" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="423" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="422" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="421" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7AFBA1B-7343-4E05-A088-EE92C857EAFC}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:M25"/>
@@ -9527,413 +10430,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C9CC5C5-F7CB-43C7-9CDC-410BE50A947C}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>10/12/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (12th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.54513888888888884</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.57638888888888884</v>
-      </c>
-      <c r="E2" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>6.1666666666666661</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>2.166666666666667</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (13th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.5625</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.59236111111111112</v>
-      </c>
-      <c r="E3" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>6.5833333333333339</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>1.7833333333333323</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (14th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.56527777777777777</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.59652777777777777</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>6.65</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>1.6833333333333327</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (15th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.49166666666666664</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.5229166666666667</v>
-      </c>
-      <c r="E5" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>4.8833333333333329</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>3.4499999999999984</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K5" s="13">
-        <f t="shared" si="4"/>
-        <v>45.000000000000078</v>
-      </c>
-      <c r="L5" s="14">
-        <f t="shared" si="5"/>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (16th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.56319444444444444</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.59375</v>
-      </c>
-      <c r="E6" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>6.6000000000000005</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>1.7499999999999991</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8.35</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="4"/>
-        <v>44</v>
-      </c>
-      <c r="L6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.716666666666661</v>
-      </c>
-      <c r="K7" s="25">
-        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>1.2999999999999985</v>
-      </c>
-      <c r="L7" s="34">
-        <f>(IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1) * 60</f>
-        <v>107.9999999999998</v>
-      </c>
-      <c r="M7" s="15"/>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.7166666666666615</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>1.7166666666666615</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="420" priority="3" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="419" priority="4" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="418" priority="8" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="417" priority="9" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="416" priority="10" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="415" priority="11" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="414" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="413" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="412" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="411" priority="6" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="410" priority="7" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F536AF-B26B-4088-9F12-A3C7FDB6B0E0}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:M25"/>
@@ -10340,7 +10837,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC499B9-050F-4A63-AD58-B03C062DE40E}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:M25"/>
@@ -10747,7 +11244,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ADA2EDE-7873-4984-BD8B-6BE6DA51A055}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:M25"/>
@@ -11146,7 +11643,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{147CAD13-550A-47AC-814D-87BFC7C1D749}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:M25"/>
@@ -11543,7 +12040,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{880CC944-ACF2-4B78-8F94-9FEAAB92C701}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:M25"/>
@@ -11946,7 +12443,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4CFE7D-7614-4F7F-B0B0-8B0AD836CA96}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:M25"/>
@@ -12343,7 +12840,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56C38E4F-E691-46C6-97FD-EC7175A0C027}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:M25"/>
@@ -12746,7 +13243,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7461D9D8-918B-4A24-B181-4C0540C55ECF}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:M25"/>
@@ -13149,7 +13646,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3005DEE3-E784-4BAF-9730-AC8A15978DE6}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:M25"/>
@@ -13552,7 +14049,413 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C9CC5C5-F7CB-43C7-9CDC-410BE50A947C}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>10/12/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (12th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.54513888888888884</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>6.1666666666666661</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.166666666666667</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (13th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.5625</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.59236111111111112</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="28"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>6.5833333333333339</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>1.7833333333333323</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (14th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.56527777777777777</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.59652777777777777</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>6.65</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>1.6833333333333327</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (15th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.49166666666666664</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>4.8833333333333329</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.4499999999999984</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>45.000000000000078</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (16th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.56319444444444444</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.59375</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>6.6000000000000005</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>1.7499999999999991</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.35</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.716666666666661</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.2999999999999985</v>
+      </c>
+      <c r="L7" s="34">
+        <f>(IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1) * 60</f>
+        <v>107.9999999999998</v>
+      </c>
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.7166666666666615</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.7166666666666615</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="420" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="419" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="418" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="417" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="416" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="415" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="414" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="413" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="412" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="411" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="410" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D473AA26-956E-44CC-A227-92587E57ACBA}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:M25"/>
@@ -13956,413 +14859,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D839D3B-74C1-4606-AD5E-3ACF14EBFDDF}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>10/05/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (5th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.55138888888888893</v>
-      </c>
-      <c r="E2" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>5.5833333333333348</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>2.7666666666666648</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.35</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>44</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-21.999999999999979</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (6th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.52361111111111114</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.55486111111111114</v>
-      </c>
-      <c r="E3" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>5.6500000000000012</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.6833333333333318</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (7th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.53472222222222221</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.56597222222222221</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>5.916666666666667</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>2.4166666666666661</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (8th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.56805555555555554</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.6</v>
-      </c>
-      <c r="E5" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>6.7166666666666668</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>1.5999999999999996</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3166666666666664</v>
-      </c>
-      <c r="K5" s="13">
-        <f t="shared" si="4"/>
-        <v>46</v>
-      </c>
-      <c r="L5" s="14">
-        <f t="shared" si="5"/>
-        <v>-19.999999999999986</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (9th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28958333333333336</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.56805555555555554</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.59861111111111109</v>
-      </c>
-      <c r="E6" s="8">
-        <v>0.66805555555555551</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>6.6833333333333318</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>1.6666666666666661</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3499999999999979</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="4"/>
-        <v>44</v>
-      </c>
-      <c r="L6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-21.999999999999872</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.683333333333323</v>
-      </c>
-      <c r="K7" s="25">
-        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>1.2666666666666666</v>
-      </c>
-      <c r="L7" s="34">
-        <f>(IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1) * 60</f>
-        <v>105.9999999999997</v>
-      </c>
-      <c r="M7" s="15"/>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.6833333333333229</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>1.6833333333333229</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="409" priority="3" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="408" priority="4" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="407" priority="8" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="406" priority="9" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="405" priority="10" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="404" priority="11" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="403" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="402" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="401" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="400" priority="6" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="399" priority="7" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DAA111-5E1D-4B97-9693-D547B2E6E4CE}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:M25"/>
@@ -14766,7 +15263,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E2ECAE-46BA-4924-85FC-E83F2A7590E3}">
   <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:M25"/>
@@ -15170,7 +15667,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCCCED9-7C1F-4E5C-BB14-2542C55B392A}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:M25"/>
@@ -15566,7 +16063,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71775678-8DD4-41DB-BC9F-367C263DFB6D}">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:M25"/>
@@ -15964,7 +16461,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3D6F94-B8B8-465C-9353-6F78C34B9117}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:M25"/>
@@ -16358,7 +16855,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2022D25-AB37-4043-9F9F-6F62C5CF4383}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:M25"/>
@@ -16735,7 +17232,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAB208D-7788-4F4C-BA6F-08A0CD669B15}">
   <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:M25"/>
@@ -17118,7 +17615,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D776AF6C-2FD4-4B22-9D2F-E02D7E857044}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:M25"/>
@@ -17501,7 +17998,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3377F8F3-7578-415F-8E55-F8837A247A0F}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:M25"/>
@@ -17882,7 +18379,413 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D839D3B-74C1-4606-AD5E-3ACF14EBFDDF}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>10/05/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (5th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.55138888888888893</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>5.5833333333333348</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>2.7666666666666648</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.35</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>44</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-21.999999999999979</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (6th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.52361111111111114</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.55486111111111114</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="28"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.6500000000000012</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.6833333333333318</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (7th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.56597222222222221</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F4" s="30">
+        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>5.916666666666667</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.4166666666666661</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>45</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (8th)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.56805555555555554</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>6.7166666666666668</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>1.5999999999999996</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3166666666666664</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>46</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-19.999999999999986</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (9th)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.28958333333333336</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.56805555555555554</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.59861111111111109</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.66805555555555551</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>6.6833333333333318</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>1.6666666666666661</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3499999999999979</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-21.999999999999872</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.683333333333323</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.2666666666666666</v>
+      </c>
+      <c r="L7" s="34">
+        <f>(IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1) * 60</f>
+        <v>105.9999999999997</v>
+      </c>
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.6833333333333229</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.6833333333333229</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="409" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="408" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="407" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="406" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="405" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="404" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="403" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="402" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="401" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="400" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="399" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCD931C-AA06-4404-8DD2-3A1635928042}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:L25"/>
@@ -18233,410 +19136,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDA9A0F6-C2E7-4667-8D20-B384B9D566A1}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>09/28/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (28th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.47986111111111113</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.51597222222222228</v>
-      </c>
-      <c r="E2" s="8">
-        <v>0.66736111111111107</v>
-      </c>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>4.6000000000000014</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.6333333333333311</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.2333333333333325</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>52.000000000000057</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-14.99999999999995</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (29th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.51597222222222228</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.54583333333333328</v>
-      </c>
-      <c r="E3" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>5.4666666666666686</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>2.9000000000000004</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3666666666666689</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>42.999999999999844</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-23.000000000000135</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (30th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.54861111111111116</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.5805555555555556</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.66736111111111107</v>
-      </c>
-      <c r="F4" s="30">
-        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>6.2500000000000018</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>2.0833333333333313</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>46</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (1st)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.50347222222222221</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.53333333333333333</v>
-      </c>
-      <c r="E5" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>5.166666666666667</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>3.1999999999999993</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3666666666666671</v>
-      </c>
-      <c r="K5" s="13">
-        <f t="shared" si="4"/>
-        <v>43.000000000000007</v>
-      </c>
-      <c r="L5" s="14">
-        <f t="shared" si="5"/>
-        <v>-23.000000000000028</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (2nd)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.375</v>
-      </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="8">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10">
-        <v>4</v>
-      </c>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>-9</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="K6" s="13" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve"> - </v>
-      </c>
-      <c r="L6" s="14" t="str">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>41.3</v>
-      </c>
-      <c r="K7" s="25">
-        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>1.9333333333333351</v>
-      </c>
-      <c r="L7" s="34">
-        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
-        <v>1.3666666666666674</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-1.2999999999999972</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>1.2999999999999972</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="398" priority="3" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="397" priority="4" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="396" priority="8" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="395" priority="9" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="394" priority="10" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="393" priority="11" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="392" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="391" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="390" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="389" priority="6" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="388" priority="7" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9BACA-BE7E-4E29-8B4C-6183BB3FCDDD}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:L25"/>
@@ -18987,7 +19487,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672B717E-C369-4345-87A7-5F55301B0739}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:L25"/>
@@ -19338,7 +19838,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D807F8E1-29A6-4379-865F-F9EC8A6B72ED}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:L25"/>
@@ -19690,6 +20190,409 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDA9A0F6-C2E7-4667-8D20-B384B9D566A1}">
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
+        <v>09/28/2026</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Mon (28th)</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.47986111111111113</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.51597222222222228</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0.66736111111111107</v>
+      </c>
+      <c r="F2" s="30">
+        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
+        <v>4</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="10">
+        <f>SUM(C2 - B2) * 24</f>
+        <v>4.6000000000000014</v>
+      </c>
+      <c r="I2" s="11">
+        <f>SUM(E2 - D2) * 24</f>
+        <v>3.6333333333333311</v>
+      </c>
+      <c r="J2" s="12">
+        <f>H2 + I2 + G2</f>
+        <v>8.2333333333333325</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
+        <v>52.000000000000057</v>
+      </c>
+      <c r="L2" s="14">
+        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
+        <v>-14.99999999999995</v>
+      </c>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Tue (29th)</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.51597222222222228</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.54583333333333328</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F3" s="30">
+        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="28"/>
+      <c r="H3" s="10">
+        <f>SUM(C3 - B3) * 24</f>
+        <v>5.4666666666666686</v>
+      </c>
+      <c r="I3" s="11">
+        <f>SUM(E3 - D3) * 24</f>
+        <v>2.9000000000000004</v>
+      </c>
+      <c r="J3" s="12">
+        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
+        <v>8.3666666666666689</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
+        <v>42.999999999999844</v>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
+        <v>-23.000000000000135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Wed (30th)</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.5805555555555556</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.66736111111111107</v>
+      </c>
+      <c r="F4" s="30">
+        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
+        <v>4</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
+        <v>6.2500000000000018</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
+        <v>2.0833333333333313</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="K4" s="13">
+        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
+        <v>46</v>
+      </c>
+      <c r="L4" s="14">
+        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
+        <v>-20.999999999999929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Thu (1st)</v>
+      </c>
+      <c r="B5" s="8">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F5" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="10">
+        <f t="shared" si="2"/>
+        <v>5.166666666666667</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="3"/>
+        <v>3.1999999999999993</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" si="4"/>
+        <v>43.000000000000007</v>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="5"/>
+        <v>-23.000000000000028</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16" t="str">
+        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
+        <v>Fri (2nd)</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F6" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G6" s="10">
+        <v>4</v>
+      </c>
+      <c r="H6" s="10">
+        <f>SUM(C6 - B6) * 24</f>
+        <v>-9</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K6" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> - </v>
+      </c>
+      <c r="L6" s="14" t="str">
+        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="19"/>
+      <c r="I7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="22">
+        <f>SUM(J2:J6)</f>
+        <v>41.3</v>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
+        <v>1.9333333333333351</v>
+      </c>
+      <c r="L7" s="34">
+        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
+        <v>1.3666666666666674</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="19"/>
+      <c r="G9" s="23"/>
+      <c r="I9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25">
+        <f>40-J7</f>
+        <v>-1.2999999999999972</v>
+      </c>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="25">
+        <f>IF(J7 &lt; 40, "-", J7-40)</f>
+        <v>1.2999999999999972</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="398" priority="3" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="397" priority="4" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="cellIs" dxfId="396" priority="8" operator="greaterThan">
+      <formula>7.99999999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="395" priority="9" operator="lessThan">
+      <formula>8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
+    <cfRule type="cellIs" dxfId="394" priority="10" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="393" priority="11" operator="greaterThan">
+      <formula>39.999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7">
+    <cfRule type="cellIs" dxfId="392" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="391" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
+    <cfRule type="cellIs" dxfId="390" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="389" priority="6" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="388" priority="7" operator="lessThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB17A34-8771-4EB9-93AD-612A5096895D}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -20092,7 +20995,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A4D2493-FA26-4C6B-B29B-2869ADDFFA07}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -20497,7 +21400,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39FCE4F4-4177-4ECC-BBBB-6DD7A08CB273}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -20890,7 +21793,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C93E5BB9-8062-4382-A731-FC67616139D4}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
@@ -21291,409 +22194,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{767FE0DE-E855-4B79-85C0-6CD6FF74CBDD}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="69.75" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn.CONCAT(MID(_xlfn.TEXTAFTER(CELL("filename", A1), "]"),5,2), "/", RIGHT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 2), "/", LEFT(_xlfn.TEXTAFTER(CELL("filename", A1), "]"), 4))</f>
-        <v>08/24/2026</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1, "ddd"), " (", DAY(A1), IF(OR(AND(DAY(A1) &gt; 23, DAY(A1) &lt; 31), AND(DAY(A1) &gt; 3, DAY(A1) &lt; 21)), "th", LOOKUP(DAY(A1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Mon (24th)</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C2" s="8">
-        <v>0.50763888888888886</v>
-      </c>
-      <c r="D2" s="8">
-        <v>0.53888888888888886</v>
-      </c>
-      <c r="E2" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F2" s="30">
-        <f>IF(G2 &gt;= 8, 4 + COUNT(B2:E2), IF(AND(G2 &gt;= 4, G2 &lt;= 7), 2 + COUNT(B2:E2), COUNT(B2:E2)))</f>
-        <v>4</v>
-      </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="10">
-        <f>SUM(C2 - B2) * 24</f>
-        <v>5.2666666666666666</v>
-      </c>
-      <c r="I2" s="11">
-        <f>SUM(E2 - D2) * 24</f>
-        <v>3.0666666666666664</v>
-      </c>
-      <c r="J2" s="12">
-        <f>H2 + I2 + G2</f>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K2" s="13">
-        <f>IF(AND(C2 &lt;&gt; "", D2 &lt;&gt; ""), (SUM(D2 - C2) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L2" s="14">
-        <f>IF(AND((B2 &lt;&gt; ""), (C2 &lt;&gt; ""), (D2 &lt;&gt; ""), (E2 &lt;&gt; "")), IF((((8 - J2) * 60) + 1) &gt; 0, (((8 - J2) * 60) + 1), (((8 - J2) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 1, "ddd"), " (", DAY(A1 + 1), IF(OR(AND(DAY(A1 + 1) &gt; 23, DAY(A1 + 1) &lt; 31), AND(DAY(A1 + 1) &gt; 3, DAY(A1 + 1) &lt; 21)), "th", LOOKUP(DAY(A1 + 1), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Tue (25th)</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.49930555555555556</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.53055555555555556</v>
-      </c>
-      <c r="E3" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F6" si="0">IF(G3 &gt;= 8, 4 + COUNT(B3:E3), IF(AND(G3 &gt;= 4, G3 &lt;= 7), 2 + COUNT(B3:E3), COUNT(B3:E3)))</f>
-        <v>4</v>
-      </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="10">
-        <f>SUM(C3 - B3) * 24</f>
-        <v>5.0666666666666673</v>
-      </c>
-      <c r="I3" s="11">
-        <f>SUM(E3 - D3) * 24</f>
-        <v>3.2666666666666657</v>
-      </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J6" si="1">H3 + I3 + G3</f>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K3" s="13">
-        <f>IF(AND(C3 &lt;&gt; "", D3 &lt;&gt; ""), (SUM(D3 - C3) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L3" s="14">
-        <f>IF(AND((B3 &lt;&gt; ""), (C3 &lt;&gt; ""), (D3 &lt;&gt; ""), (E3 &lt;&gt; "")), IF((((8 - J3) * 60) + 1) &gt; 0, (((8 - J3) * 60) + 1), (((8 - J3) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 2, "ddd"), " (", DAY(A1 + 2), IF(OR(AND(DAY(A1 + 2) &gt; 23, DAY(A1 + 2) &lt; 31), AND(DAY(A1 + 2) &gt; 3, DAY(A1 + 2) &lt; 21)), "th", LOOKUP(DAY(A1 + 2), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Wed (26th)</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.5229166666666667</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.5541666666666667</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F4" s="30">
-        <f>IF(G4 &gt;= 8, 4 + COUNT(B4:E4), IF(AND(G4 &gt;= 4, G4 &lt;= 7), 2 + COUNT(B4:E4), COUNT(B4:E4)))</f>
-        <v>4</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4:H5" si="2">SUM(C4 - B4) * 24</f>
-        <v>5.6333333333333346</v>
-      </c>
-      <c r="I4" s="11">
-        <f t="shared" ref="I4:I6" si="3">SUM(E4 - D4) * 24</f>
-        <v>2.6999999999999984</v>
-      </c>
-      <c r="J4" s="12">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K6" si="4">IF(AND(C4 &lt;&gt; "", D4 &lt;&gt; ""), (SUM(D4 - C4) * 1440), " - ")</f>
-        <v>45</v>
-      </c>
-      <c r="L4" s="14">
-        <f t="shared" ref="L4:L5" si="5">IF(AND((B4 &lt;&gt; ""), (C4 &lt;&gt; ""), (D4 &lt;&gt; ""), (E4 &lt;&gt; "")), IF((((8 - J4) * 60) + 1) &gt; 0, (((8 - J4) * 60) + 1), (((8 - J4) * 60) - 1)), "-")</f>
-        <v>-20.999999999999929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 3, "ddd"), " (", DAY(A1 + 3), IF(OR(AND(DAY(A1 + 3) &gt; 23, DAY(A1 + 3) &lt; 31), AND(DAY(A1 + 3) &gt; 3, DAY(A1 + 3) &lt; 21)), "th", LOOKUP(DAY(A1 + 3), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Thu (27th)</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.5131944444444444</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.54374999999999996</v>
-      </c>
-      <c r="E5" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="10">
-        <f t="shared" si="2"/>
-        <v>5.3999999999999995</v>
-      </c>
-      <c r="I5" s="11">
-        <f t="shared" si="3"/>
-        <v>2.95</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="1"/>
-        <v>8.35</v>
-      </c>
-      <c r="K5" s="13">
-        <f t="shared" si="4"/>
-        <v>44</v>
-      </c>
-      <c r="L5" s="14">
-        <f t="shared" si="5"/>
-        <v>-21.999999999999979</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="str">
-        <f ca="1">_xlfn.CONCAT(TEXT(A1 + 4, "ddd"), " (", DAY(A1 + 4), IF(OR(AND(DAY(A1 + 4) &gt; 23, DAY(A1 + 4) &lt; 31), AND(DAY(A1 + 4) &gt; 3, DAY(A1 + 4) &lt; 21)), "th", LOOKUP(DAY(A1 + 4), {1,"st";2,"nd";3,"rd";21,"st";22,"nd";23,"rd";31,"st"})), ")")</f>
-        <v>Fri (28th)</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.28819444444444442</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.51458333333333328</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.54513888888888884</v>
-      </c>
-      <c r="E6" s="8">
-        <v>0.71736111111111112</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10">
-        <f>SUM(C6 - B6) * 24</f>
-        <v>5.4333333333333327</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="3"/>
-        <v>4.1333333333333346</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>9.5666666666666664</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="4"/>
-        <v>44</v>
-      </c>
-      <c r="L6" s="14">
-        <f>IF(AND((B6 &lt;&gt; ""), (C6 &lt;&gt; ""), (D6 &lt;&gt; ""), (E6 &lt;&gt; "")), IF((((8 - J6) * 60) + 1) &gt; 0, (((8 - J6) * 60) + 1), (((8 - J6) * 60) - 1)), "-")</f>
-        <v>-94.999999999999986</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="19"/>
-      <c r="I7" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="22">
-        <f>SUM(J2:J6)</f>
-        <v>42.916666666666657</v>
-      </c>
-      <c r="K7" s="25">
-        <f>IF(SUM(K2:K6) &lt;&gt; 0, ((60*5) - SUM(K2:K6)) / 60, 0)</f>
-        <v>1.2833333333333334</v>
-      </c>
-      <c r="L7" s="34">
-        <f>IF(SUM(L2:L6) &lt;&gt; 0, (SUM(L2:L6)/ 60), 0) * -1</f>
-        <v>2.999999999999996</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="G9" s="23"/>
-      <c r="I9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="25">
-        <f>40-J7</f>
-        <v>-2.9166666666666572</v>
-      </c>
-      <c r="K9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="I10" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="25">
-        <f>IF(J7 &lt; 40, "-", J7-40)</f>
-        <v>2.9166666666666572</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-    </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-    </row>
-    <row r="21" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-    </row>
-    <row r="23" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-    </row>
-    <row r="24" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="11:12" x14ac:dyDescent="0.35">
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="cellIs" dxfId="343" priority="3" operator="greaterThan">
-      <formula>3</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="342" priority="4" operator="lessThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="cellIs" dxfId="341" priority="8" operator="greaterThan">
-      <formula>7.99999999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="340" priority="9" operator="lessThan">
-      <formula>8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J7">
-    <cfRule type="cellIs" dxfId="339" priority="10" operator="lessThan">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="338" priority="11" operator="greaterThan">
-      <formula>39.999999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="337" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="336" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="cellIs" dxfId="335" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="334" priority="6" operator="greaterThan">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="333" priority="7" operator="lessThan">
-      <formula>0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>